--- a/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Evolution_Production.xlsx
+++ b/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Evolution_Production.xlsx
@@ -2,34 +2,34 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rcc26c78f80084596"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="R2b2d0daa65654eb3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="R2852da9645f14c8b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="R110c003b5e124c8c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="R83baaab4a2a4470e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="Rdfaddddc76804a0d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="R8dcb5c967c574b20"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="R9142de52334c4592"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="R981bdc04561c4b18"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="R400598a6f2fb4057"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="R13208b35d0134989"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="Read99a7d8c824a2d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R589917effe9842e0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="Rb52836a681b04f0b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="R4a083ead36734dd3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R5fa051818c0d4026"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="Raeb424dd854742db"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="Re0e12374db7341a2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="R2b711a7a94314009"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="R8b793683afcb4b36"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="R45ae9d350c4a4e6d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="Reb82c3954a2f4612"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="R67e6759f5b8a411e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="Rc160243be07e4da8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="R1ae87b6ca7ab4df6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="Rdb96f7a299754876"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="Redbf6ddd4ebc4066"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="R06d5b6055bcc48de"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Ref8da14d5c174291"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="R00075bfd6eda4eea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="Rb80973683d51416c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="R055f5de0fb934b7d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="R732799aab53643d6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="Rd66d8aa90a694082"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="Rc12349e6b87940a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="Rf535ad4f275d4936"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="R1bb3edf44d0a476a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="R6b45b52bc165458c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="R5bba45d4e8c743aa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="R8b83b7fd80074b25"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="Rff8a251197564f49"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="R049e1bc80b2940a5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="R2e321147539f4a2d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R0b7bf4a07df64309"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="R88c46a6cc38a4190"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="R3bc3721903ac407f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="R88e849d0638d49c6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="R100608afceeb4c68"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="Raa78634bc45341b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="R67b6f9a0d0e44867"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="R91d9cc58999d4c6d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="R857eea84b5e34ace"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="Rce0f342c8f1546bb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="Re3d0de76b38c4de6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="Rf534406493534b2a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="R285ab1c1c9c74c3a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -174,7 +174,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="45">
+  <x:cellXfs count="43">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -230,12 +230,6 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="top" wrapText="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
@@ -2156,7 +2150,7 @@
       <x:c r="A5" s="2" t="str">
         <x:v>Fiches suivies</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:f>SUM(B10:B35)</x:f>
         <x:v>122</x:v>
       </x:c>
@@ -2164,7 +2158,7 @@
       <x:c r="D5" s="2" t="str">
         <x:v>Intégrés</x:v>
       </x:c>
-      <x:c r="E5" s="33" t="n">
+      <x:c r="E5" s="31" t="n">
         <x:f>SUM(E10:F35)</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2172,7 +2166,7 @@
       <x:c r="G5" s="2" t="str">
         <x:v>À vérifier</x:v>
       </x:c>
-      <x:c r="H5" s="33" t="n">
+      <x:c r="H5" s="31" t="n">
         <x:f>SUM(H10:H35)</x:f>
         <x:v>3</x:v>
       </x:c>
@@ -2180,7 +2174,7 @@
       <x:c r="J5" s="2" t="str">
         <x:v>Extrapolations</x:v>
       </x:c>
-      <x:c r="K5" s="33" t="n">
+      <x:c r="K5" s="31" t="n">
         <x:f>SUM(I10:I35)</x:f>
         <x:v>98</x:v>
       </x:c>
@@ -2203,7 +2197,7 @@
       <x:c r="M6" s="2"/>
     </x:row>
     <x:row r="7" ht="22" customHeight="1">
-      <x:c r="A7" s="34" t="str">
+      <x:c r="A7" s="32" t="str">
         <x:v>Défini = spécification. Établi = référence documentée. Les colonnes d’adaptation restent des propositions.</x:v>
       </x:c>
       <x:c r="B7" s="2"/>
@@ -2235,95 +2229,95 @@
       <x:c r="M8" s="2"/>
     </x:row>
     <x:row r="9" ht="34" customHeight="1">
-      <x:c r="A9" s="30" t="str">
+      <x:c r="A9" s="28" t="str">
         <x:v>Domaine</x:v>
       </x:c>
-      <x:c r="B9" s="31" t="str">
+      <x:c r="B9" s="29" t="str">
         <x:v>Total</x:v>
       </x:c>
-      <x:c r="C9" s="31" t="str">
+      <x:c r="C9" s="29" t="str">
         <x:v>Défini</x:v>
       </x:c>
-      <x:c r="D9" s="31" t="str">
+      <x:c r="D9" s="29" t="str">
         <x:v>Prototype</x:v>
       </x:c>
-      <x:c r="E9" s="31" t="str">
+      <x:c r="E9" s="29" t="str">
         <x:v>Intégré</x:v>
       </x:c>
-      <x:c r="F9" s="31" t="str">
+      <x:c r="F9" s="29" t="str">
         <x:v>Validé</x:v>
       </x:c>
-      <x:c r="G9" s="31" t="str">
+      <x:c r="G9" s="29" t="str">
         <x:v>Établi</x:v>
       </x:c>
-      <x:c r="H9" s="31" t="str">
+      <x:c r="H9" s="29" t="str">
         <x:v>À vérifier</x:v>
       </x:c>
-      <x:c r="I9" s="31" t="str">
+      <x:c r="I9" s="29" t="str">
         <x:v>Extrapolation</x:v>
       </x:c>
-      <x:c r="J9" s="31" t="str">
+      <x:c r="J9" s="29" t="str">
         <x:v>Coupé attesté</x:v>
       </x:c>
-      <x:c r="K9" s="31" t="str">
+      <x:c r="K9" s="29" t="str">
         <x:v>Concept abandonné</x:v>
       </x:c>
-      <x:c r="L9" s="31" t="str">
+      <x:c r="L9" s="29" t="str">
         <x:v>Allégation écartée</x:v>
       </x:c>
-      <x:c r="M9" s="32" t="str">
+      <x:c r="M9" s="30" t="str">
         <x:v>Priorité P0</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="22" customHeight="1">
-      <x:c r="A10" s="35" t="str">
+      <x:c r="A10" s="33" t="str">
         <x:v>Personnages</x:v>
       </x:c>
-      <x:c r="B10" s="39" t="n">
+      <x:c r="B10" s="37" t="n">
         <x:f>COUNTA('Personnages'!$A$7:$A$10)</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C10" s="39" t="n">
+      <x:c r="C10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$C$7:$C$10,"Défini")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D10" s="39" t="n">
+      <x:c r="D10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$C$7:$C$10,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E10" s="39" t="n">
+      <x:c r="E10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$C$7:$C$10,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F10" s="39" t="n">
+      <x:c r="F10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$C$7:$C$10,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G10" s="39" t="n">
+      <x:c r="G10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$10,"Établi")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="H10" s="39" t="n">
+      <x:c r="H10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$10,"À vérifier")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I10" s="39" t="n">
+      <x:c r="I10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$10,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J10" s="39" t="n">
+      <x:c r="J10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$10,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K10" s="39" t="n">
+      <x:c r="K10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$10,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L10" s="39" t="n">
+      <x:c r="L10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$D$7:$D$10,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M10" s="39" t="n">
+      <x:c r="M10" s="37" t="n">
         <x:f>COUNTIFS('Personnages'!$E$7:$E$10,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2332,104 +2326,104 @@
       <x:c r="A11" s="2" t="str">
         <x:v>PNJ</x:v>
       </x:c>
-      <x:c r="B11" s="40" t="n">
+      <x:c r="B11" s="38" t="n">
         <x:f>COUNTA('PNJ'!$A$7:$A$9)</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C11" s="40" t="n">
+      <x:c r="C11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$C$7:$C$9,"Défini")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D11" s="40" t="n">
+      <x:c r="D11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$C$7:$C$9,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E11" s="40" t="n">
+      <x:c r="E11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$C$7:$C$9,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F11" s="40" t="n">
+      <x:c r="F11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$C$7:$C$9,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G11" s="40" t="n">
+      <x:c r="G11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$9,"Établi")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="H11" s="40" t="n">
+      <x:c r="H11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$9,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I11" s="40" t="n">
+      <x:c r="I11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$9,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J11" s="40" t="n">
+      <x:c r="J11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$9,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K11" s="40" t="n">
+      <x:c r="K11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$9,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L11" s="40" t="n">
+      <x:c r="L11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$D$7:$D$9,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M11" s="40" t="n">
+      <x:c r="M11" s="38" t="n">
         <x:f>COUNTIFS('PNJ'!$E$7:$E$9,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="22" customHeight="1">
-      <x:c r="A12" s="35" t="str">
+      <x:c r="A12" s="33" t="str">
         <x:v>Espèces et factions</x:v>
       </x:c>
-      <x:c r="B12" s="39" t="n">
+      <x:c r="B12" s="37" t="n">
         <x:f>COUNTA('Especes_factions'!$A$7:$A$16)</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="C12" s="39" t="n">
+      <x:c r="C12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$C$7:$C$16,"Défini")</x:f>
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D12" s="39" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$C$7:$C$16,"Prototype")</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E12" s="39" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$C$7:$C$16,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F12" s="39" t="n">
+      <x:c r="F12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$C$7:$C$16,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G12" s="39" t="n">
+      <x:c r="G12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$16,"Établi")</x:f>
         <x:v>10</x:v>
       </x:c>
-      <x:c r="H12" s="39" t="n">
+      <x:c r="H12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$16,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I12" s="39" t="n">
+      <x:c r="I12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$16,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J12" s="39" t="n">
+      <x:c r="J12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$16,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K12" s="39" t="n">
+      <x:c r="K12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$16,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L12" s="39" t="n">
+      <x:c r="L12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$D$7:$D$16,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M12" s="39" t="n">
+      <x:c r="M12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$E$7:$E$16,"P0")</x:f>
         <x:v>4</x:v>
       </x:c>
@@ -2438,104 +2432,104 @@
       <x:c r="A13" s="2" t="str">
         <x:v>Mondes</x:v>
       </x:c>
-      <x:c r="B13" s="40" t="n">
+      <x:c r="B13" s="38" t="n">
         <x:f>COUNTA('Mondes'!$A$7:$A$10)</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C13" s="40" t="n">
+      <x:c r="C13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$C$7:$C$10,"Défini")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D13" s="40" t="n">
+      <x:c r="D13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$C$7:$C$10,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E13" s="40" t="n">
+      <x:c r="E13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$C$7:$C$10,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F13" s="40" t="n">
+      <x:c r="F13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$C$7:$C$10,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G13" s="40" t="n">
+      <x:c r="G13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$10,"Établi")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="H13" s="40" t="n">
+      <x:c r="H13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$10,"À vérifier")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I13" s="40" t="n">
+      <x:c r="I13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$10,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J13" s="40" t="n">
+      <x:c r="J13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$10,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K13" s="40" t="n">
+      <x:c r="K13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$10,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L13" s="40" t="n">
+      <x:c r="L13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$D$7:$D$10,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M13" s="40" t="n">
+      <x:c r="M13" s="38" t="n">
         <x:f>COUNTIFS('Mondes'!$E$7:$E$10,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="22" customHeight="1">
-      <x:c r="A14" s="35" t="str">
+      <x:c r="A14" s="33" t="str">
         <x:v>Zones</x:v>
       </x:c>
-      <x:c r="B14" s="39" t="n">
+      <x:c r="B14" s="37" t="n">
         <x:f>COUNTA('Zones'!$A$7:$A$10)</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C14" s="39" t="n">
+      <x:c r="C14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$C$7:$C$10,"Défini")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D14" s="39" t="n">
+      <x:c r="D14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$C$7:$C$10,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E14" s="39" t="n">
+      <x:c r="E14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$C$7:$C$10,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F14" s="39" t="n">
+      <x:c r="F14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$C$7:$C$10,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G14" s="39" t="n">
+      <x:c r="G14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$10,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H14" s="39" t="n">
+      <x:c r="H14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$10,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I14" s="39" t="n">
+      <x:c r="I14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$10,"Extrapolation")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="J14" s="39" t="n">
+      <x:c r="J14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$10,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K14" s="39" t="n">
+      <x:c r="K14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$10,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L14" s="39" t="n">
+      <x:c r="L14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$D$7:$D$10,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M14" s="39" t="n">
+      <x:c r="M14" s="37" t="n">
         <x:f>COUNTIFS('Zones'!$E$7:$E$10,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2544,104 +2538,104 @@
       <x:c r="A15" s="2" t="str">
         <x:v>Liaisons</x:v>
       </x:c>
-      <x:c r="B15" s="40" t="n">
+      <x:c r="B15" s="38" t="n">
         <x:f>COUNTA('Liaisons'!$A$7:$A$10)</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C15" s="40" t="n">
+      <x:c r="C15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$C$7:$C$10,"Défini")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D15" s="40" t="n">
+      <x:c r="D15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$C$7:$C$10,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E15" s="40" t="n">
+      <x:c r="E15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$C$7:$C$10,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F15" s="40" t="n">
+      <x:c r="F15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$C$7:$C$10,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G15" s="40" t="n">
+      <x:c r="G15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$10,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H15" s="40" t="n">
+      <x:c r="H15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$10,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I15" s="40" t="n">
+      <x:c r="I15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$10,"Extrapolation")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="J15" s="40" t="n">
+      <x:c r="J15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$10,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K15" s="40" t="n">
+      <x:c r="K15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$10,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L15" s="40" t="n">
+      <x:c r="L15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$D$7:$D$10,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M15" s="40" t="n">
+      <x:c r="M15" s="38" t="n">
         <x:f>COUNTIFS('Liaisons'!$E$7:$E$10,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="22" customHeight="1">
-      <x:c r="A16" s="35" t="str">
+      <x:c r="A16" s="33" t="str">
         <x:v>Décors</x:v>
       </x:c>
-      <x:c r="B16" s="39" t="n">
+      <x:c r="B16" s="37" t="n">
         <x:f>COUNTA('Decors'!$A$7:$A$10)</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C16" s="39" t="n">
+      <x:c r="C16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$C$7:$C$10,"Défini")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D16" s="39" t="n">
+      <x:c r="D16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$C$7:$C$10,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E16" s="39" t="n">
+      <x:c r="E16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$C$7:$C$10,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F16" s="39" t="n">
+      <x:c r="F16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$C$7:$C$10,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G16" s="39" t="n">
+      <x:c r="G16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$10,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H16" s="39" t="n">
+      <x:c r="H16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$10,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I16" s="39" t="n">
+      <x:c r="I16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$10,"Extrapolation")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="J16" s="39" t="n">
+      <x:c r="J16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$10,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K16" s="39" t="n">
+      <x:c r="K16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$10,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L16" s="39" t="n">
+      <x:c r="L16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$D$7:$D$10,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M16" s="39" t="n">
+      <x:c r="M16" s="37" t="n">
         <x:f>COUNTIFS('Decors'!$E$7:$E$10,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2650,104 +2644,104 @@
       <x:c r="A17" s="2" t="str">
         <x:v>Props</x:v>
       </x:c>
-      <x:c r="B17" s="40" t="n">
+      <x:c r="B17" s="38" t="n">
         <x:f>COUNTA('Props'!$A$7:$A$12)</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C17" s="40" t="n">
+      <x:c r="C17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$C$7:$C$12,"Défini")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D17" s="40" t="n">
+      <x:c r="D17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$C$7:$C$12,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E17" s="40" t="n">
+      <x:c r="E17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$C$7:$C$12,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F17" s="40" t="n">
+      <x:c r="F17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$C$7:$C$12,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G17" s="40" t="n">
+      <x:c r="G17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$12,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H17" s="40" t="n">
+      <x:c r="H17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$12,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I17" s="40" t="n">
+      <x:c r="I17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$12,"Extrapolation")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="J17" s="40" t="n">
+      <x:c r="J17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$12,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K17" s="40" t="n">
+      <x:c r="K17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$12,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L17" s="40" t="n">
+      <x:c r="L17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$D$7:$D$12,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M17" s="40" t="n">
+      <x:c r="M17" s="38" t="n">
         <x:f>COUNTIFS('Props'!$E$7:$E$12,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="22" customHeight="1">
-      <x:c r="A18" s="35" t="str">
+      <x:c r="A18" s="33" t="str">
         <x:v>Ennemis et boss</x:v>
       </x:c>
-      <x:c r="B18" s="39" t="n">
+      <x:c r="B18" s="37" t="n">
         <x:f>COUNTA('Ennemis_boss'!$A$7:$A$9)</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="C18" s="39" t="n">
+      <x:c r="C18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$C$7:$C$9,"Défini")</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="D18" s="39" t="n">
+      <x:c r="D18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$C$7:$C$9,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E18" s="39" t="n">
+      <x:c r="E18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$C$7:$C$9,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F18" s="39" t="n">
+      <x:c r="F18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$C$7:$C$9,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G18" s="39" t="n">
+      <x:c r="G18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$9,"Établi")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="H18" s="39" t="n">
+      <x:c r="H18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$9,"À vérifier")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I18" s="39" t="n">
+      <x:c r="I18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$9,"Extrapolation")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="J18" s="39" t="n">
+      <x:c r="J18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$9,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K18" s="39" t="n">
+      <x:c r="K18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$9,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L18" s="39" t="n">
+      <x:c r="L18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$D$7:$D$9,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M18" s="39" t="n">
+      <x:c r="M18" s="37" t="n">
         <x:f>COUNTIFS('Ennemis_boss'!$E$7:$E$9,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2756,104 +2750,104 @@
       <x:c r="A19" s="2" t="str">
         <x:v>Missions</x:v>
       </x:c>
-      <x:c r="B19" s="40" t="n">
+      <x:c r="B19" s="38" t="n">
         <x:f>COUNTA('Missions'!$A$7:$A$12)</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C19" s="40" t="n">
+      <x:c r="C19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$C$7:$C$12,"Défini")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D19" s="40" t="n">
+      <x:c r="D19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$C$7:$C$12,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E19" s="40" t="n">
+      <x:c r="E19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$C$7:$C$12,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F19" s="40" t="n">
+      <x:c r="F19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$C$7:$C$12,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G19" s="40" t="n">
+      <x:c r="G19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$12,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H19" s="40" t="n">
+      <x:c r="H19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$12,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I19" s="40" t="n">
+      <x:c r="I19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$12,"Extrapolation")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="J19" s="40" t="n">
+      <x:c r="J19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$12,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K19" s="40" t="n">
+      <x:c r="K19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$12,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L19" s="40" t="n">
+      <x:c r="L19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$D$7:$D$12,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M19" s="40" t="n">
+      <x:c r="M19" s="38" t="n">
         <x:f>COUNTIFS('Missions'!$E$7:$E$12,"P0")</x:f>
         <x:v>6</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="22" customHeight="1">
-      <x:c r="A20" s="35" t="str">
+      <x:c r="A20" s="33" t="str">
         <x:v>Secondaires et DLC</x:v>
       </x:c>
-      <x:c r="B20" s="39" t="n">
+      <x:c r="B20" s="37" t="n">
         <x:f>COUNTA('Secondaires_DLC'!$A$7:$A$12)</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C20" s="39" t="n">
+      <x:c r="C20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$C$7:$C$12,"Défini")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D20" s="39" t="n">
+      <x:c r="D20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$C$7:$C$12,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E20" s="39" t="n">
+      <x:c r="E20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$C$7:$C$12,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F20" s="39" t="n">
+      <x:c r="F20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$C$7:$C$12,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G20" s="39" t="n">
+      <x:c r="G20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$12,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H20" s="39" t="n">
+      <x:c r="H20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$12,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I20" s="39" t="n">
+      <x:c r="I20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$12,"Extrapolation")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="J20" s="39" t="n">
+      <x:c r="J20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$12,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K20" s="39" t="n">
+      <x:c r="K20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$12,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L20" s="39" t="n">
+      <x:c r="L20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$D$7:$D$12,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M20" s="39" t="n">
+      <x:c r="M20" s="37" t="n">
         <x:f>COUNTIFS('Secondaires_DLC'!$E$7:$E$12,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2862,104 +2856,104 @@
       <x:c r="A21" s="2" t="str">
         <x:v>Choix et relations</x:v>
       </x:c>
-      <x:c r="B21" s="40" t="n">
+      <x:c r="B21" s="38" t="n">
         <x:f>COUNTA('Choix_relations'!$A$7:$A$12)</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C21" s="40" t="n">
+      <x:c r="C21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$C$7:$C$12,"Défini")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D21" s="40" t="n">
+      <x:c r="D21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$C$7:$C$12,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E21" s="40" t="n">
+      <x:c r="E21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$C$7:$C$12,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F21" s="40" t="n">
+      <x:c r="F21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$C$7:$C$12,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G21" s="40" t="n">
+      <x:c r="G21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$12,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H21" s="40" t="n">
+      <x:c r="H21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$12,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I21" s="40" t="n">
+      <x:c r="I21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$12,"Extrapolation")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="J21" s="40" t="n">
+      <x:c r="J21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$12,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K21" s="40" t="n">
+      <x:c r="K21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$12,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L21" s="40" t="n">
+      <x:c r="L21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$D$7:$D$12,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M21" s="40" t="n">
+      <x:c r="M21" s="38" t="n">
         <x:f>COUNTIFS('Choix_relations'!$E$7:$E$12,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="22" customHeight="1">
-      <x:c r="A22" s="35" t="str">
+      <x:c r="A22" s="33" t="str">
         <x:v>Dialogues</x:v>
       </x:c>
-      <x:c r="B22" s="39" t="n">
+      <x:c r="B22" s="37" t="n">
         <x:f>COUNTA('Dialogues'!$A$7:$A$12)</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C22" s="39" t="n">
+      <x:c r="C22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$C$7:$C$12,"Défini")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D22" s="39" t="n">
+      <x:c r="D22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$C$7:$C$12,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E22" s="39" t="n">
+      <x:c r="E22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$C$7:$C$12,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F22" s="39" t="n">
+      <x:c r="F22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$C$7:$C$12,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G22" s="39" t="n">
+      <x:c r="G22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$12,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H22" s="39" t="n">
+      <x:c r="H22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$12,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I22" s="39" t="n">
+      <x:c r="I22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$12,"Extrapolation")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="J22" s="39" t="n">
+      <x:c r="J22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$12,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K22" s="39" t="n">
+      <x:c r="K22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$12,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L22" s="39" t="n">
+      <x:c r="L22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$D$7:$D$12,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M22" s="39" t="n">
+      <x:c r="M22" s="37" t="n">
         <x:f>COUNTIFS('Dialogues'!$E$7:$E$12,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -2968,104 +2962,104 @@
       <x:c r="A23" s="2" t="str">
         <x:v>Cinématiques</x:v>
       </x:c>
-      <x:c r="B23" s="40" t="n">
+      <x:c r="B23" s="38" t="n">
         <x:f>COUNTA('Cinematiques'!$A$7:$A$12)</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C23" s="40" t="n">
+      <x:c r="C23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$C$7:$C$12,"Défini")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D23" s="40" t="n">
+      <x:c r="D23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$C$7:$C$12,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E23" s="40" t="n">
+      <x:c r="E23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$C$7:$C$12,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F23" s="40" t="n">
+      <x:c r="F23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$C$7:$C$12,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G23" s="40" t="n">
+      <x:c r="G23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$12,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H23" s="40" t="n">
+      <x:c r="H23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$12,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I23" s="40" t="n">
+      <x:c r="I23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$12,"Extrapolation")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="J23" s="40" t="n">
+      <x:c r="J23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$12,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K23" s="40" t="n">
+      <x:c r="K23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$12,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L23" s="40" t="n">
+      <x:c r="L23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$D$7:$D$12,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M23" s="40" t="n">
+      <x:c r="M23" s="38" t="n">
         <x:f>COUNTIFS('Cinematiques'!$E$7:$E$12,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="22" customHeight="1">
-      <x:c r="A24" s="35" t="str">
+      <x:c r="A24" s="33" t="str">
         <x:v>Armes</x:v>
       </x:c>
-      <x:c r="B24" s="39" t="n">
+      <x:c r="B24" s="37" t="n">
         <x:f>COUNTA('Armes'!$A$7:$A$7)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C24" s="39" t="n">
+      <x:c r="C24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$C$7:$C$7,"Défini")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D24" s="39" t="n">
+      <x:c r="D24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$C$7:$C$7,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E24" s="39" t="n">
+      <x:c r="E24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$C$7:$C$7,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F24" s="39" t="n">
+      <x:c r="F24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$C$7:$C$7,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G24" s="39" t="n">
+      <x:c r="G24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$7,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H24" s="39" t="n">
+      <x:c r="H24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$7,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I24" s="39" t="n">
+      <x:c r="I24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$7,"Extrapolation")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J24" s="39" t="n">
+      <x:c r="J24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$7,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K24" s="39" t="n">
+      <x:c r="K24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$7,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L24" s="39" t="n">
+      <x:c r="L24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$D$7:$D$7,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M24" s="39" t="n">
+      <x:c r="M24" s="37" t="n">
         <x:f>COUNTIFS('Armes'!$E$7:$E$7,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3074,104 +3068,104 @@
       <x:c r="A25" s="2" t="str">
         <x:v>Armures et équipement</x:v>
       </x:c>
-      <x:c r="B25" s="40" t="n">
+      <x:c r="B25" s="38" t="n">
         <x:f>COUNTA('Armures_equipement'!$A$7:$A$7)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C25" s="40" t="n">
+      <x:c r="C25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$C$7:$C$7,"Défini")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D25" s="40" t="n">
+      <x:c r="D25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$C$7:$C$7,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E25" s="40" t="n">
+      <x:c r="E25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$C$7:$C$7,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F25" s="40" t="n">
+      <x:c r="F25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$C$7:$C$7,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G25" s="40" t="n">
+      <x:c r="G25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$7,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H25" s="40" t="n">
+      <x:c r="H25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$7,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I25" s="40" t="n">
+      <x:c r="I25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$7,"Extrapolation")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J25" s="40" t="n">
+      <x:c r="J25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$7,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K25" s="40" t="n">
+      <x:c r="K25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$7,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L25" s="40" t="n">
+      <x:c r="L25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$D$7:$D$7,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M25" s="40" t="n">
+      <x:c r="M25" s="38" t="n">
         <x:f>COUNTIFS('Armures_equipement'!$E$7:$E$7,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="22" customHeight="1">
-      <x:c r="A26" s="35" t="str">
+      <x:c r="A26" s="33" t="str">
         <x:v>Pouvoirs</x:v>
       </x:c>
-      <x:c r="B26" s="39" t="n">
+      <x:c r="B26" s="37" t="n">
         <x:f>COUNTA('Pouvoirs'!$A$7:$A$7)</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="C26" s="39" t="n">
+      <x:c r="C26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$C$7:$C$7,"Défini")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="D26" s="39" t="n">
+      <x:c r="D26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$C$7:$C$7,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E26" s="39" t="n">
+      <x:c r="E26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$C$7:$C$7,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F26" s="39" t="n">
+      <x:c r="F26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$C$7:$C$7,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G26" s="39" t="n">
+      <x:c r="G26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$7,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H26" s="39" t="n">
+      <x:c r="H26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$7,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I26" s="39" t="n">
+      <x:c r="I26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$7,"Extrapolation")</x:f>
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J26" s="39" t="n">
+      <x:c r="J26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$7,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K26" s="39" t="n">
+      <x:c r="K26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$7,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L26" s="39" t="n">
+      <x:c r="L26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$D$7:$D$7,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M26" s="39" t="n">
+      <x:c r="M26" s="37" t="n">
         <x:f>COUNTIFS('Pouvoirs'!$E$7:$E$7,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3180,104 +3174,104 @@
       <x:c r="A27" s="2" t="str">
         <x:v>Movesets alliés</x:v>
       </x:c>
-      <x:c r="B27" s="40" t="n">
+      <x:c r="B27" s="38" t="n">
         <x:f>COUNTA('Movesets_allies'!$A$7:$A$8)</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C27" s="40" t="n">
+      <x:c r="C27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$C$7:$C$8,"Défini")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D27" s="40" t="n">
+      <x:c r="D27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$C$7:$C$8,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E27" s="40" t="n">
+      <x:c r="E27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$C$7:$C$8,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F27" s="40" t="n">
+      <x:c r="F27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$C$7:$C$8,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G27" s="40" t="n">
+      <x:c r="G27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$8,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H27" s="40" t="n">
+      <x:c r="H27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$8,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I27" s="40" t="n">
+      <x:c r="I27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$8,"Extrapolation")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J27" s="40" t="n">
+      <x:c r="J27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$8,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K27" s="40" t="n">
+      <x:c r="K27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$8,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L27" s="40" t="n">
+      <x:c r="L27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$D$7:$D$8,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M27" s="40" t="n">
+      <x:c r="M27" s="38" t="n">
         <x:f>COUNTIFS('Movesets_allies'!$E$7:$E$8,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="22" customHeight="1">
-      <x:c r="A28" s="35" t="str">
+      <x:c r="A28" s="33" t="str">
         <x:v>Movesets ennemis</x:v>
       </x:c>
-      <x:c r="B28" s="39" t="n">
+      <x:c r="B28" s="37" t="n">
         <x:f>COUNTA('Movesets_ennemis'!$A$7:$A$12)</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C28" s="39" t="n">
+      <x:c r="C28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$C$7:$C$12,"Défini")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D28" s="39" t="n">
+      <x:c r="D28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$C$7:$C$12,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E28" s="39" t="n">
+      <x:c r="E28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$C$7:$C$12,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F28" s="39" t="n">
+      <x:c r="F28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$C$7:$C$12,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G28" s="39" t="n">
+      <x:c r="G28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$12,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H28" s="39" t="n">
+      <x:c r="H28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$12,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I28" s="39" t="n">
+      <x:c r="I28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$12,"Extrapolation")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="J28" s="39" t="n">
+      <x:c r="J28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$12,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K28" s="39" t="n">
+      <x:c r="K28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$12,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L28" s="39" t="n">
+      <x:c r="L28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$D$7:$D$12,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M28" s="39" t="n">
+      <x:c r="M28" s="37" t="n">
         <x:f>COUNTIFS('Movesets_ennemis'!$E$7:$E$12,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3286,104 +3280,104 @@
       <x:c r="A29" s="2" t="str">
         <x:v>Animations</x:v>
       </x:c>
-      <x:c r="B29" s="40" t="n">
+      <x:c r="B29" s="38" t="n">
         <x:f>COUNTA('Animations'!$A$7:$A$13)</x:f>
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C29" s="40" t="n">
+      <x:c r="C29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$C$7:$C$13,"Défini")</x:f>
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D29" s="40" t="n">
+      <x:c r="D29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$C$7:$C$13,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E29" s="40" t="n">
+      <x:c r="E29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$C$7:$C$13,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F29" s="40" t="n">
+      <x:c r="F29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$C$7:$C$13,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G29" s="40" t="n">
+      <x:c r="G29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$13,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H29" s="40" t="n">
+      <x:c r="H29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$13,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I29" s="40" t="n">
+      <x:c r="I29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$13,"Extrapolation")</x:f>
         <x:v>7</x:v>
       </x:c>
-      <x:c r="J29" s="40" t="n">
+      <x:c r="J29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$13,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K29" s="40" t="n">
+      <x:c r="K29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$13,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L29" s="40" t="n">
+      <x:c r="L29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$D$7:$D$13,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M29" s="40" t="n">
+      <x:c r="M29" s="38" t="n">
         <x:f>COUNTIFS('Animations'!$E$7:$E$13,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="22" customHeight="1">
-      <x:c r="A30" s="35" t="str">
+      <x:c r="A30" s="33" t="str">
         <x:v>Sprites</x:v>
       </x:c>
-      <x:c r="B30" s="39" t="n">
+      <x:c r="B30" s="37" t="n">
         <x:f>COUNTA('Sprites'!$A$7:$A$13)</x:f>
         <x:v>7</x:v>
       </x:c>
-      <x:c r="C30" s="39" t="n">
+      <x:c r="C30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$C$7:$C$13,"Défini")</x:f>
         <x:v>7</x:v>
       </x:c>
-      <x:c r="D30" s="39" t="n">
+      <x:c r="D30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$C$7:$C$13,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E30" s="39" t="n">
+      <x:c r="E30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$C$7:$C$13,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F30" s="39" t="n">
+      <x:c r="F30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$C$7:$C$13,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G30" s="39" t="n">
+      <x:c r="G30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$13,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H30" s="39" t="n">
+      <x:c r="H30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$13,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I30" s="39" t="n">
+      <x:c r="I30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$13,"Extrapolation")</x:f>
         <x:v>7</x:v>
       </x:c>
-      <x:c r="J30" s="39" t="n">
+      <x:c r="J30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$13,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K30" s="39" t="n">
+      <x:c r="K30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$13,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L30" s="39" t="n">
+      <x:c r="L30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$D$7:$D$13,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M30" s="39" t="n">
+      <x:c r="M30" s="37" t="n">
         <x:f>COUNTIFS('Sprites'!$E$7:$E$13,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3392,104 +3386,104 @@
       <x:c r="A31" s="2" t="str">
         <x:v>VFX</x:v>
       </x:c>
-      <x:c r="B31" s="40" t="n">
+      <x:c r="B31" s="38" t="n">
         <x:f>COUNTA('VFX'!$A$7:$A$12)</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="C31" s="40" t="n">
+      <x:c r="C31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$C$7:$C$12,"Défini")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D31" s="40" t="n">
+      <x:c r="D31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$C$7:$C$12,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E31" s="40" t="n">
+      <x:c r="E31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$C$7:$C$12,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F31" s="40" t="n">
+      <x:c r="F31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$C$7:$C$12,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G31" s="40" t="n">
+      <x:c r="G31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$12,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H31" s="40" t="n">
+      <x:c r="H31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$12,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I31" s="40" t="n">
+      <x:c r="I31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$12,"Extrapolation")</x:f>
         <x:v>6</x:v>
       </x:c>
-      <x:c r="J31" s="40" t="n">
+      <x:c r="J31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$12,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K31" s="40" t="n">
+      <x:c r="K31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$12,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L31" s="40" t="n">
+      <x:c r="L31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$D$7:$D$12,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M31" s="40" t="n">
+      <x:c r="M31" s="38" t="n">
         <x:f>COUNTIFS('VFX'!$E$7:$E$12,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="22" customHeight="1">
-      <x:c r="A32" s="35" t="str">
+      <x:c r="A32" s="33" t="str">
         <x:v>Audio</x:v>
       </x:c>
-      <x:c r="B32" s="39" t="n">
+      <x:c r="B32" s="37" t="n">
         <x:f>COUNTA('Audio'!$A$7:$A$10)</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C32" s="39" t="n">
+      <x:c r="C32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$C$7:$C$10,"Défini")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D32" s="39" t="n">
+      <x:c r="D32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$C$7:$C$10,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E32" s="39" t="n">
+      <x:c r="E32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$C$7:$C$10,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F32" s="39" t="n">
+      <x:c r="F32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$C$7:$C$10,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G32" s="39" t="n">
+      <x:c r="G32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$10,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H32" s="39" t="n">
+      <x:c r="H32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$10,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I32" s="39" t="n">
+      <x:c r="I32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$10,"Extrapolation")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="J32" s="39" t="n">
+      <x:c r="J32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$10,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K32" s="39" t="n">
+      <x:c r="K32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$10,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L32" s="39" t="n">
+      <x:c r="L32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$D$7:$D$10,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M32" s="39" t="n">
+      <x:c r="M32" s="37" t="n">
         <x:f>COUNTIFS('Audio'!$E$7:$E$10,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
@@ -3498,104 +3492,104 @@
       <x:c r="A33" s="2" t="str">
         <x:v>Systèmes et UI</x:v>
       </x:c>
-      <x:c r="B33" s="40" t="n">
+      <x:c r="B33" s="38" t="n">
         <x:f>COUNTA('UI_systemes'!$A$7:$A$10)</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="C33" s="40" t="n">
+      <x:c r="C33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$C$7:$C$10,"Défini")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="D33" s="40" t="n">
+      <x:c r="D33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$C$7:$C$10,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E33" s="40" t="n">
+      <x:c r="E33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$C$7:$C$10,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F33" s="40" t="n">
+      <x:c r="F33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$C$7:$C$10,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G33" s="40" t="n">
+      <x:c r="G33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$10,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H33" s="40" t="n">
+      <x:c r="H33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$10,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I33" s="40" t="n">
+      <x:c r="I33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$10,"Extrapolation")</x:f>
         <x:v>4</x:v>
       </x:c>
-      <x:c r="J33" s="40" t="n">
+      <x:c r="J33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$10,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K33" s="40" t="n">
+      <x:c r="K33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$10,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L33" s="40" t="n">
+      <x:c r="L33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$D$7:$D$10,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M33" s="40" t="n">
+      <x:c r="M33" s="38" t="n">
         <x:f>COUNTIFS('UI_systemes'!$E$7:$E$10,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="22" customHeight="1">
-      <x:c r="A34" s="35" t="str">
+      <x:c r="A34" s="33" t="str">
         <x:v>QA</x:v>
       </x:c>
-      <x:c r="B34" s="39" t="n">
+      <x:c r="B34" s="37" t="n">
         <x:f>COUNTA('QA'!$A$7:$A$15)</x:f>
         <x:v>9</x:v>
       </x:c>
-      <x:c r="C34" s="39" t="n">
+      <x:c r="C34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$C$7:$C$15,"Défini")</x:f>
         <x:v>9</x:v>
       </x:c>
-      <x:c r="D34" s="39" t="n">
+      <x:c r="D34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$C$7:$C$15,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E34" s="39" t="n">
+      <x:c r="E34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$C$7:$C$15,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F34" s="39" t="n">
+      <x:c r="F34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$C$7:$C$15,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G34" s="39" t="n">
+      <x:c r="G34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$15,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H34" s="39" t="n">
+      <x:c r="H34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$15,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I34" s="39" t="n">
+      <x:c r="I34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$15,"Extrapolation")</x:f>
         <x:v>9</x:v>
       </x:c>
-      <x:c r="J34" s="39" t="n">
+      <x:c r="J34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$15,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K34" s="39" t="n">
+      <x:c r="K34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$15,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L34" s="39" t="n">
+      <x:c r="L34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$D$7:$D$15,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M34" s="39" t="n">
+      <x:c r="M34" s="37" t="n">
         <x:f>COUNTIFS('QA'!$E$7:$E$15,"P0")</x:f>
         <x:v>9</x:v>
       </x:c>
@@ -3604,119 +3598,119 @@
       <x:c r="A35" s="2" t="str">
         <x:v>Continuité</x:v>
       </x:c>
-      <x:c r="B35" s="40" t="n">
+      <x:c r="B35" s="38" t="n">
         <x:f>COUNTA('Continuite'!$A$7:$A$8)</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="C35" s="40" t="n">
+      <x:c r="C35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$C$7:$C$8,"Défini")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D35" s="40" t="n">
+      <x:c r="D35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$C$7:$C$8,"Prototype")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E35" s="40" t="n">
+      <x:c r="E35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$C$7:$C$8,"Intégré")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F35" s="40" t="n">
+      <x:c r="F35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$C$7:$C$8,"Validé")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G35" s="40" t="n">
+      <x:c r="G35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$8,"Établi")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="H35" s="40" t="n">
+      <x:c r="H35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$8,"À vérifier")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I35" s="40" t="n">
+      <x:c r="I35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$8,"Extrapolation")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="J35" s="40" t="n">
+      <x:c r="J35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$8,"Coupé attesté")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K35" s="40" t="n">
+      <x:c r="K35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$8,"Concept abandonné")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L35" s="40" t="n">
+      <x:c r="L35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$D$7:$D$8,"Allégation écartée")</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M35" s="40" t="n">
+      <x:c r="M35" s="38" t="n">
         <x:f>COUNTIFS('Continuite'!$E$7:$E$8,"P0")</x:f>
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="22" customHeight="1">
       <x:c r="A36" s="2"/>
-      <x:c r="B36" s="40"/>
-      <x:c r="C36" s="40"/>
-      <x:c r="D36" s="40"/>
-      <x:c r="E36" s="40"/>
-      <x:c r="F36" s="40"/>
-      <x:c r="G36" s="40"/>
-      <x:c r="H36" s="40"/>
-      <x:c r="I36" s="40"/>
-      <x:c r="J36" s="40"/>
-      <x:c r="K36" s="40"/>
-      <x:c r="L36" s="40"/>
-      <x:c r="M36" s="40"/>
+      <x:c r="B36" s="38"/>
+      <x:c r="C36" s="38"/>
+      <x:c r="D36" s="38"/>
+      <x:c r="E36" s="38"/>
+      <x:c r="F36" s="38"/>
+      <x:c r="G36" s="38"/>
+      <x:c r="H36" s="38"/>
+      <x:c r="I36" s="38"/>
+      <x:c r="J36" s="38"/>
+      <x:c r="K36" s="38"/>
+      <x:c r="L36" s="38"/>
+      <x:c r="M36" s="38"/>
     </x:row>
     <x:row r="37" ht="28" customHeight="1">
-      <x:c r="A37" s="23" t="str">
+      <x:c r="A37" s="21" t="str">
         <x:v>TOTAL</x:v>
       </x:c>
-      <x:c r="B37" s="41" t="n">
+      <x:c r="B37" s="39" t="n">
         <x:f>SUM(B10:B35)</x:f>
         <x:v>122</x:v>
       </x:c>
-      <x:c r="C37" s="41" t="n">
+      <x:c r="C37" s="39" t="n">
         <x:f>SUM(C10:C35)</x:f>
-        <x:v>122</x:v>
-      </x:c>
-      <x:c r="D37" s="41" t="n">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="D37" s="39" t="n">
         <x:f>SUM(D10:D35)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E37" s="41" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="E37" s="39" t="n">
         <x:f>SUM(E10:E35)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="F37" s="41" t="n">
+      <x:c r="F37" s="39" t="n">
         <x:f>SUM(F10:F35)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="G37" s="41" t="n">
+      <x:c r="G37" s="39" t="n">
         <x:f>SUM(G10:G35)</x:f>
         <x:v>21</x:v>
       </x:c>
-      <x:c r="H37" s="41" t="n">
+      <x:c r="H37" s="39" t="n">
         <x:f>SUM(H10:H35)</x:f>
         <x:v>3</x:v>
       </x:c>
-      <x:c r="I37" s="41" t="n">
+      <x:c r="I37" s="39" t="n">
         <x:f>SUM(I10:I35)</x:f>
         <x:v>98</x:v>
       </x:c>
-      <x:c r="J37" s="41" t="n">
+      <x:c r="J37" s="39" t="n">
         <x:f>SUM(J10:J35)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="K37" s="41" t="n">
+      <x:c r="K37" s="39" t="n">
         <x:f>SUM(K10:K35)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L37" s="41" t="n">
+      <x:c r="L37" s="39" t="n">
         <x:f>SUM(L10:L35)</x:f>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="M37" s="41" t="n">
+      <x:c r="M37" s="39" t="n">
         <x:f>SUM(M10:M35)</x:f>
         <x:v>19</x:v>
       </x:c>
@@ -3940,61 +3934,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -4048,10 +4042,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>EVO-S-EVA</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Eva_Cor%C3%A9</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>L’adversaire ou groupe est attesté selon la source; le combat ATB et ses réglages sont entièrement proposés.</x:v>
       </x:c>
     </x:row>
@@ -4105,10 +4099,10 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>EVO-S-AUTHOR4</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://farawaypress.com/comics/masseffectevolution/masseffectevolution4/</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="S8" s="7" t="str">
         <x:v>L’adversaire ou groupe est attesté selon la source; le combat ATB et ses réglages sont entièrement proposés.</x:v>
       </x:c>
     </x:row>
@@ -4162,10 +4156,10 @@
       <x:c r="Q9" s="9" t="str">
         <x:v>EVO-S-AUTHOR3</x:v>
       </x:c>
-      <x:c r="R9" s="20" t="str">
+      <x:c r="R9" s="9" t="str">
         <x:v>https://farawaypress.com/comics/masseffectevolution/masseffectevolution3/</x:v>
       </x:c>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="S9" s="9" t="str">
         <x:v>L’adversaire ou groupe est attesté selon la source; le combat ATB et ses réglages sont entièrement proposés.</x:v>
       </x:c>
     </x:row>
@@ -4201,7 +4195,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd2c78932065446e7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R02de9d748f7543c9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4341,61 +4335,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -4449,8 +4443,8 @@
         <x:v>Conception originale rattachée à Evolution #1</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -4502,8 +4496,8 @@
         <x:v>Conception originale rattachée à Evolution #1</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -4555,8 +4549,8 @@
         <x:v>Conception originale rattachée à Transition Evolution #1 → #2</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -4608,8 +4602,8 @@
         <x:v>Conception originale rattachée à Evolution #2</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="68" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -4661,8 +4655,8 @@
         <x:v>Conception originale rattachée à Evolution #3</x:v>
       </x:c>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="68" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -4714,8 +4708,8 @@
         <x:v>Conception originale rattachée à Evolution #4</x:v>
       </x:c>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D12">
@@ -4749,7 +4743,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbed197b0f7b949a6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2f1bcb26c01b47eb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4889,61 +4883,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -4997,8 +4991,8 @@
         <x:v>Ajout original; cette tâche n’est pas attestée dans le comic.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -5050,8 +5044,8 @@
         <x:v>Ajout original; cette tâche n’est pas attestée dans le comic.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -5103,8 +5097,8 @@
         <x:v>Ajout original; cette tâche n’est pas attestée dans le comic.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -5156,8 +5150,8 @@
         <x:v>Ajout original; cette tâche n’est pas attestée dans le comic.</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="54" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -5209,8 +5203,8 @@
         <x:v>Ajout original; cette tâche n’est pas attestée dans le comic.</x:v>
       </x:c>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="54" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -5262,8 +5256,8 @@
         <x:v>Ajout original; cette tâche n’est pas attestée dans le comic.</x:v>
       </x:c>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D12">
@@ -5297,7 +5291,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re88449b0130f4eba"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0ef560463dba4161"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5437,61 +5431,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -5545,8 +5539,8 @@
         <x:v>Bifurcation de gameplay originale, pas un choix présent dans l’œuvre.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -5598,8 +5592,8 @@
         <x:v>Bifurcation de gameplay originale, pas un choix présent dans l’œuvre.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -5651,8 +5645,8 @@
         <x:v>Bifurcation de gameplay originale, pas un choix présent dans l’œuvre.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -5704,8 +5698,8 @@
         <x:v>Bifurcation de gameplay originale, pas un choix présent dans l’œuvre.</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="54" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -5757,8 +5751,8 @@
         <x:v>Bifurcation de gameplay originale, pas un choix présent dans l’œuvre.</x:v>
       </x:c>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="54" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -5810,8 +5804,8 @@
         <x:v>Bifurcation de gameplay originale, pas un choix présent dans l’œuvre.</x:v>
       </x:c>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D12">
@@ -5845,7 +5839,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4c20831d34d34db1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra97eea96c6854335"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5985,61 +5979,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -6093,8 +6087,8 @@
         <x:v>Écriture originale à partir des thèmes, sans transcrire les bulles.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -6146,8 +6140,8 @@
         <x:v>Écriture originale à partir des thèmes, sans transcrire les bulles.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -6199,8 +6193,8 @@
         <x:v>Écriture originale à partir des thèmes, sans transcrire les bulles.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -6252,8 +6246,8 @@
         <x:v>Écriture originale à partir des thèmes, sans transcrire les bulles.</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="54" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -6305,8 +6299,8 @@
         <x:v>Écriture originale à partir des thèmes, sans transcrire les bulles.</x:v>
       </x:c>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="54" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -6358,8 +6352,8 @@
         <x:v>Écriture originale à partir des thèmes, sans transcrire les bulles.</x:v>
       </x:c>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D12">
@@ -6393,7 +6387,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ref72777ae10c40db"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re9bbf1169aff4f47"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6533,61 +6527,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -6639,8 +6633,8 @@
         <x:v>Découpage original pour sprites 2D sur décor 3D.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -6690,8 +6684,8 @@
         <x:v>Découpage original pour sprites 2D sur décor 3D.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -6741,8 +6735,8 @@
         <x:v>Découpage original pour sprites 2D sur décor 3D.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -6792,8 +6786,8 @@
         <x:v>Découpage original pour sprites 2D sur décor 3D.</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="54" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -6843,8 +6837,8 @@
         <x:v>Découpage original pour sprites 2D sur décor 3D.</x:v>
       </x:c>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="54" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -6894,8 +6888,8 @@
         <x:v>Découpage original pour sprites 2D sur décor 3D.</x:v>
       </x:c>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D12">
@@ -6929,7 +6923,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2a22aac0baa04690"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcbd3ea89b26548c7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7069,61 +7063,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -7175,8 +7169,8 @@
         <x:v>Création de gameplay et direction visuelle originales; modèle exact à vérifier si une arme source est évoquée.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D7">
@@ -7210,7 +7204,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2c63cae545b147ba"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdaff3fe6f6164cf2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7350,61 +7344,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -7456,8 +7450,8 @@
         <x:v>Création de gameplay et direction visuelle originales; modèle exact à vérifier si une arme source est évoquée.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D7">
@@ -7491,7 +7485,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd0d56a0fe02248fd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R294f97c7f7cc4ada"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7631,61 +7625,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -7737,8 +7731,8 @@
         <x:v>Création de gameplay et direction visuelle originales; modèle exact à vérifier si une arme source est évoquée.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D7">
@@ -7772,7 +7766,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc60c5036f9cb497a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8e14d12b30c54d80"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7912,61 +7906,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -8020,8 +8014,8 @@
         <x:v>Adaptation originale du rôle; pas un pouvoir officiel du comic.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -8073,8 +8067,8 @@
         <x:v>Adaptation originale du rôle; pas un pouvoir officiel du comic.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D8">
@@ -8108,7 +8102,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra3f7fd2ab26c46c7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7a45620c17bb43fc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8248,61 +8242,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -8356,10 +8350,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>EVO-S-AUTHOR2</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://farawaypress.com/comics/masseffectevolution/masseffectevolution2/</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>Le rôle dans la source ne prouve ni recrutement jouable ni disponibilité permanente.</x:v>
       </x:c>
     </x:row>
@@ -8413,10 +8407,10 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>EVO-S-EVA</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Eva_Cor%C3%A9</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="S8" s="7" t="str">
         <x:v>Le rôle dans la source ne prouve ni recrutement jouable ni disponibilité permanente.</x:v>
       </x:c>
     </x:row>
@@ -8470,10 +8464,10 @@
       <x:c r="Q9" s="9" t="str">
         <x:v>EVO-S-AUTHOR3</x:v>
       </x:c>
-      <x:c r="R9" s="20" t="str">
+      <x:c r="R9" s="9" t="str">
         <x:v>https://farawaypress.com/comics/masseffectevolution/masseffectevolution3/</x:v>
       </x:c>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="S9" s="9" t="str">
         <x:v>Le rôle dans la source ne prouve ni recrutement jouable ni disponibilité permanente.</x:v>
       </x:c>
     </x:row>
@@ -8527,10 +8521,10 @@
       <x:c r="Q10" s="7" t="str">
         <x:v>EVO-S-AUTHOR3</x:v>
       </x:c>
-      <x:c r="R10" s="21" t="str">
+      <x:c r="R10" s="7" t="str">
         <x:v>https://farawaypress.com/comics/masseffectevolution/masseffectevolution3/</x:v>
       </x:c>
-      <x:c r="S10" s="21" t="str">
+      <x:c r="S10" s="7" t="str">
         <x:v>Le rôle dans la source ne prouve ni recrutement jouable ni disponibilité permanente.</x:v>
       </x:c>
     </x:row>
@@ -8566,7 +8560,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7c4952a8f19540a8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9ab42619236045f7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8706,61 +8700,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -8814,8 +8808,8 @@
         <x:v>Pattern original; pas de valeur numérique canon.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -8867,8 +8861,8 @@
         <x:v>Pattern original; pas de valeur numérique canon.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -8920,8 +8914,8 @@
         <x:v>Pattern original; pas de valeur numérique canon.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -8973,8 +8967,8 @@
         <x:v>Pattern original; pas de valeur numérique canon.</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="54" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -9026,8 +9020,8 @@
         <x:v>Pattern original; pas de valeur numérique canon.</x:v>
       </x:c>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="54" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -9079,8 +9073,8 @@
         <x:v>Pattern original; pas de valeur numérique canon.</x:v>
       </x:c>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D12">
@@ -9114,7 +9108,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rca15a4f48bd5449e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb688d2de175044fe"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9254,61 +9248,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -9360,8 +9354,8 @@
         <x:v>Conception originale, aucune cadence extraite du comic.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -9411,8 +9405,8 @@
         <x:v>Conception originale, aucune cadence extraite du comic.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="82" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -9462,8 +9456,8 @@
         <x:v>Conception originale, aucune cadence extraite du comic.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="82" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -9513,8 +9507,8 @@
         <x:v>Conception originale, aucune cadence extraite du comic.</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="68" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -9564,8 +9558,8 @@
         <x:v>Conception originale, aucune cadence extraite du comic.</x:v>
       </x:c>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="68" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -9615,8 +9609,8 @@
         <x:v>Conception originale, aucune cadence extraite du comic.</x:v>
       </x:c>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="68" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -9666,8 +9660,8 @@
         <x:v>Conception originale, aucune cadence extraite du comic.</x:v>
       </x:c>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D13">
@@ -9701,7 +9695,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R51ba87865ea84413"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra09338c9a8a5420b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9841,61 +9835,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -9945,8 +9939,8 @@
         <x:v>Conception originale; référence visuelle du personnage à contrôler.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -9994,8 +9988,8 @@
         <x:v>Conception originale; référence visuelle du personnage à contrôler.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -10043,8 +10037,8 @@
         <x:v>Conception originale; référence visuelle du personnage à contrôler.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -10092,8 +10086,8 @@
         <x:v>Conception originale; référence visuelle du personnage à contrôler.</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="68" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -10141,8 +10135,8 @@
         <x:v>Conception originale; référence visuelle du personnage à contrôler.</x:v>
       </x:c>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="82" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -10190,8 +10184,8 @@
         <x:v>Conception originale; référence visuelle du personnage à contrôler.</x:v>
       </x:c>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="54" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -10239,8 +10233,8 @@
         <x:v>Conception originale; référence visuelle du personnage à contrôler.</x:v>
       </x:c>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D13">
@@ -10274,7 +10268,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rac449b6fd06e4e84"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0a9b345fdae24363"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10414,61 +10408,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -10520,8 +10514,8 @@
         <x:v>VFX original; intensité et timing à régler au prototype.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -10571,8 +10565,8 @@
         <x:v>VFX original; intensité et timing à régler au prototype.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -10622,8 +10616,8 @@
         <x:v>VFX original; intensité et timing à régler au prototype.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -10673,8 +10667,8 @@
         <x:v>VFX original; intensité et timing à régler au prototype.</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="54" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -10724,8 +10718,8 @@
         <x:v>VFX original; intensité et timing à régler au prototype.</x:v>
       </x:c>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="54" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -10775,8 +10769,8 @@
         <x:v>VFX original; intensité et timing à régler au prototype.</x:v>
       </x:c>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D12">
@@ -10810,7 +10804,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re53ba59edbae415e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc237b08d3fc244cd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10950,61 +10944,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -11058,8 +11052,8 @@
         <x:v>Création sonore originale; aucune piste commerciale requise.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -11111,8 +11105,8 @@
         <x:v>Création sonore originale; aucune piste commerciale requise.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -11164,8 +11158,8 @@
         <x:v>Création sonore originale; aucune piste commerciale requise.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -11217,8 +11211,8 @@
         <x:v>Création sonore originale; aucune piste commerciale requise.</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D10">
@@ -11252,7 +11246,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9f04f8f6441b4efe"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R813ce140fd764fdf"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11392,61 +11386,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -11494,8 +11488,8 @@
         <x:v>Règle originale de production; les ancrages de continuité sont documentés dans les fiches REF.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -11541,8 +11535,8 @@
         <x:v>Règle originale de production; les ancrages de continuité sont documentés dans les fiches REF.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -11588,8 +11582,8 @@
         <x:v>Règle originale de production; les ancrages de continuité sont documentés dans les fiches REF.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -11635,8 +11629,8 @@
         <x:v>Règle originale de production; les ancrages de continuité sont documentés dans les fiches REF.</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D10">
@@ -11670,7 +11664,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0c7cd7a404574665"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R621f3d6d438241a3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11810,61 +11804,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -11912,8 +11906,8 @@
         <x:v>Critère de production original, pas une validation déjà obtenue.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -11959,8 +11953,8 @@
         <x:v>Critère de production original, pas une validation déjà obtenue.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -12006,8 +12000,8 @@
         <x:v>Critère de production original, pas une validation déjà obtenue.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -12053,8 +12047,8 @@
         <x:v>Critère de production original, pas une validation déjà obtenue.</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="68" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -12100,8 +12094,8 @@
         <x:v>Critère de production original, pas une validation déjà obtenue.</x:v>
       </x:c>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="68" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -12147,8 +12141,8 @@
         <x:v>Critère de production original, pas une validation déjà obtenue.</x:v>
       </x:c>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
     <x:row r="13" ht="54" customHeight="1">
       <x:c r="A13" s="18" t="str">
@@ -12192,8 +12186,8 @@
         <x:v>Règle originale de production; les ancrages de continuité sont documentés dans les fiches REF.</x:v>
       </x:c>
       <x:c r="Q13" s="9" t="str"/>
-      <x:c r="R13" s="20" t="str"/>
-      <x:c r="S13" s="20" t="str"/>
+      <x:c r="R13" s="9" t="str"/>
+      <x:c r="S13" s="9" t="str"/>
     </x:row>
     <x:row r="14" ht="54" customHeight="1">
       <x:c r="A14" s="19" t="str">
@@ -12237,8 +12231,8 @@
         <x:v>Règle originale de production; les ancrages de continuité sont documentés dans les fiches REF.</x:v>
       </x:c>
       <x:c r="Q14" s="7" t="str"/>
-      <x:c r="R14" s="21" t="str"/>
-      <x:c r="S14" s="21" t="str"/>
+      <x:c r="R14" s="7" t="str"/>
+      <x:c r="S14" s="7" t="str"/>
     </x:row>
     <x:row r="15" ht="54" customHeight="1">
       <x:c r="A15" s="18" t="str">
@@ -12282,8 +12276,8 @@
         <x:v>Règle originale de production; les ancrages de continuité sont documentés dans les fiches REF.</x:v>
       </x:c>
       <x:c r="Q15" s="9" t="str"/>
-      <x:c r="R15" s="20" t="str"/>
-      <x:c r="S15" s="20" t="str"/>
+      <x:c r="R15" s="9" t="str"/>
+      <x:c r="S15" s="9" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D15">
@@ -12317,7 +12311,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6613893cdadb4f48"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf6ed1dc41fcf4913"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12457,61 +12451,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -12557,8 +12551,8 @@
         <x:v>Règle originale de production; les ancrages de continuité sont documentés dans les fiches REF.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -12602,8 +12596,8 @@
         <x:v>Règle originale de production; les ancrages de continuité sont documentés dans les fiches REF.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D8">
@@ -12637,7 +12631,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R18723599a5814835"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf8dc5d86474b4632"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12702,10 +12696,10 @@
       <x:c r="F5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Champ</x:v>
       </x:c>
-      <x:c r="B6" s="32" t="str">
+      <x:c r="B6" s="30" t="str">
         <x:v>Définition</x:v>
       </x:c>
       <x:c r="C6" s="2"/>
@@ -12749,12 +12743,12 @@
       <x:c r="E9" s="2"/>
       <x:c r="F9" s="2"/>
     </x:row>
-    <x:row r="10" ht="68" customHeight="1">
+    <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="7" t="str">
         <x:v>Projet</x:v>
       </x:c>
       <x:c r="B10" s="7" t="str">
-        <x:v>Adaptation de production en actes courts : résistance, conséquences d’un contact, confrontation au projet de Desolas et raccord vers une nouvelle identité. Faits éditoriaux brefs; systèmes proposés distincts de la continuité.</x:v>
+        <x:v>122 fiches de production ; 4 fiches au stade Prototype de portée partielle. Les autres livrables restent des spécifications ; aucun achèvement intégral 1:1 revendiqué.</x:v>
       </x:c>
       <x:c r="C10" s="2"/>
       <x:c r="D10" s="2"/>
@@ -12773,11 +12767,11 @@
       <x:c r="E11" s="2"/>
       <x:c r="F11" s="2"/>
     </x:row>
-    <x:row r="12" ht="40" customHeight="1">
+    <x:row r="12" ht="30" customHeight="1">
       <x:c r="A12" s="7" t="str">
         <x:v>Date de référence</x:v>
       </x:c>
-      <x:c r="B12" s="44" t="d">
+      <x:c r="B12" s="42" t="d">
         <x:v>2026-10-22T12:00:00.000Z</x:v>
       </x:c>
       <x:c r="C12" s="2"/>
@@ -12930,22 +12924,22 @@
       <x:c r="F25" s="2"/>
     </x:row>
     <x:row r="26" ht="34" customHeight="1">
-      <x:c r="A26" s="30" t="str">
+      <x:c r="A26" s="28" t="str">
         <x:v>Source</x:v>
       </x:c>
-      <x:c r="B26" s="31" t="str">
+      <x:c r="B26" s="29" t="str">
         <x:v>Titre</x:v>
       </x:c>
-      <x:c r="C26" s="31" t="str">
+      <x:c r="C26" s="29" t="str">
         <x:v>Type</x:v>
       </x:c>
-      <x:c r="D26" s="31" t="str">
+      <x:c r="D26" s="29" t="str">
         <x:v>URL</x:v>
       </x:c>
-      <x:c r="E26" s="31" t="str">
+      <x:c r="E26" s="29" t="str">
         <x:v>Périmètre</x:v>
       </x:c>
-      <x:c r="F26" s="32" t="str">
+      <x:c r="F26" s="30" t="str">
         <x:v>Accès et limites</x:v>
       </x:c>
     </x:row>
@@ -13094,13 +13088,13 @@
       <x:c r="F35" s="2"/>
     </x:row>
     <x:row r="36" ht="34" customHeight="1">
-      <x:c r="A36" s="30" t="str">
+      <x:c r="A36" s="28" t="str">
         <x:v>Domaine</x:v>
       </x:c>
-      <x:c r="B36" s="31" t="str">
+      <x:c r="B36" s="29" t="str">
         <x:v>Couverture actuelle</x:v>
       </x:c>
-      <x:c r="C36" s="32" t="str">
+      <x:c r="C36" s="30" t="str">
         <x:v>Travail restant</x:v>
       </x:c>
       <x:c r="D36" s="2"/>
@@ -13471,10 +13465,16 @@
       <x:c r="E62" s="2"/>
       <x:c r="F62" s="2"/>
     </x:row>
-    <x:row r="63" ht="22" customHeight="1">
-      <x:c r="A63" s="2"/>
-      <x:c r="B63" s="2"/>
-      <x:c r="C63" s="2"/>
+    <x:row r="63" ht="96" customHeight="1">
+      <x:c r="A63" s="6" t="str">
+        <x:v>Complément pouvoirs, modules et lectures</x:v>
+      </x:c>
+      <x:c r="B63" s="6" t="str">
+        <x:v>0 fiches de pouvoirs utilisées, 0 familles de modules préparables et 4 références consultables dans une lecture documentaire. Les chemins et preuves sont inscrits sur les seules lignes Prototype.</x:v>
+      </x:c>
+      <x:c r="C63" s="6" t="str">
+        <x:v>Arbres et progression complets, modèles et rangs exacts, campagnes et dialogues intégraux, niveaux et ressources visuelles propres à l’œuvre restent à réaliser ou vérifier. Les références lues ne rendent pas leurs personnages jouables.</x:v>
+      </x:c>
       <x:c r="D63" s="2"/>
       <x:c r="E63" s="2"/>
       <x:c r="F63" s="2"/>
@@ -14030,6 +14030,14 @@
       <x:c r="D132" s="2"/>
       <x:c r="E132" s="2"/>
       <x:c r="F132" s="2"/>
+    </x:row>
+    <x:row r="133" ht="22" customHeight="1">
+      <x:c r="A133" s="2"/>
+      <x:c r="B133" s="2"/>
+      <x:c r="C133" s="2"/>
+      <x:c r="D133" s="2"/>
+      <x:c r="E133" s="2"/>
+      <x:c r="F133" s="2"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14171,61 +14179,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -14279,10 +14287,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>EVO-S-AUTHOR2</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://farawaypress.com/comics/masseffectevolution/masseffectevolution2/</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>Le rôle dans la source ne prouve ni recrutement jouable ni disponibilité permanente.</x:v>
       </x:c>
     </x:row>
@@ -14336,10 +14344,10 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>EVO-S-AUTHOR1</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://farawaypress.com/comics/masseffectevolution/masseffectevolution1/</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="S8" s="7" t="str">
         <x:v>Le rôle dans la source ne prouve ni recrutement jouable ni disponibilité permanente.</x:v>
       </x:c>
     </x:row>
@@ -14393,10 +14401,10 @@
       <x:c r="Q9" s="9" t="str">
         <x:v>EVO-S-AUTHOR2</x:v>
       </x:c>
-      <x:c r="R9" s="20" t="str">
+      <x:c r="R9" s="9" t="str">
         <x:v>https://farawaypress.com/comics/masseffectevolution/masseffectevolution2/</x:v>
       </x:c>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="S9" s="9" t="str">
         <x:v>Le rôle dans la source ne prouve ni recrutement jouable ni disponibilité permanente.</x:v>
       </x:c>
     </x:row>
@@ -14432,7 +14440,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7c46b4fbfd5d4e16"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1c314a50d05c4ca9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14459,7 +14467,7 @@
     <x:col min="16" max="16" width="45" hidden="0" customWidth="1"/>
     <x:col min="17" max="17" width="24" hidden="0" customWidth="1"/>
     <x:col min="18" max="18" width="101" hidden="0" customWidth="1"/>
-    <x:col min="19" max="19" width="73" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="250" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="22" customHeight="1">
@@ -14572,61 +14580,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -14672,10 +14680,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>EVO-S-BOOK</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://www.penguinrandomhouse.com/books/241664/mass-effect-volume-2-evolution-by-mac-walters-various-artists/</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>Fait résumé brièvement; aucun dialogue ni découpage intégral du comic reproduit.</x:v>
       </x:c>
     </x:row>
@@ -14721,10 +14729,10 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>EVO-S-AUTHOR1</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://farawaypress.com/comics/masseffectevolution/masseffectevolution1/</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="S8" s="7" t="str">
         <x:v>Fait résumé brièvement; aucun dialogue ni découpage intégral du comic reproduit.</x:v>
       </x:c>
     </x:row>
@@ -14770,10 +14778,10 @@
       <x:c r="Q9" s="9" t="str">
         <x:v>EVO-S-AUTHOR3</x:v>
       </x:c>
-      <x:c r="R9" s="20" t="str">
+      <x:c r="R9" s="9" t="str">
         <x:v>https://farawaypress.com/comics/masseffectevolution/masseffectevolution3/</x:v>
       </x:c>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="S9" s="9" t="str">
         <x:v>Fait résumé brièvement; aucun dialogue ni découpage intégral du comic reproduit.</x:v>
       </x:c>
     </x:row>
@@ -14819,10 +14827,10 @@
       <x:c r="Q10" s="7" t="str">
         <x:v>EVO-S-AUTHOR4</x:v>
       </x:c>
-      <x:c r="R10" s="21" t="str">
+      <x:c r="R10" s="7" t="str">
         <x:v>https://farawaypress.com/comics/masseffectevolution/masseffectevolution4/</x:v>
       </x:c>
-      <x:c r="S10" s="21" t="str">
+      <x:c r="S10" s="7" t="str">
         <x:v>Fait résumé brièvement; aucun dialogue ni découpage intégral du comic reproduit.</x:v>
       </x:c>
     </x:row>
@@ -14868,10 +14876,10 @@
       <x:c r="Q11" s="9" t="str">
         <x:v>EVO-S-AUTHOR1</x:v>
       </x:c>
-      <x:c r="R11" s="20" t="str">
+      <x:c r="R11" s="9" t="str">
         <x:v>https://farawaypress.com/comics/masseffectevolution/masseffectevolution1/</x:v>
       </x:c>
-      <x:c r="S11" s="20" t="str">
+      <x:c r="S11" s="9" t="str">
         <x:v>Ne remplace pas la lecture du numéro.</x:v>
       </x:c>
     </x:row>
@@ -14917,14 +14925,14 @@
       <x:c r="Q12" s="7" t="str">
         <x:v>EVO-S-AUTHOR1</x:v>
       </x:c>
-      <x:c r="R12" s="21" t="str">
+      <x:c r="R12" s="7" t="str">
         <x:v>https://farawaypress.com/comics/masseffectevolution/masseffectevolution1/</x:v>
       </x:c>
-      <x:c r="S12" s="21" t="str">
+      <x:c r="S12" s="7" t="str">
         <x:v>Ne remplace pas la lecture du numéro.</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="54" customHeight="1">
+    <x:row r="13" ht="82" customHeight="1">
       <x:c r="A13" s="18" t="str">
         <x:v>EVO-SC-AFTERWAR-REF</x:v>
       </x:c>
@@ -14932,7 +14940,7 @@
         <x:v>Après la guerre</x:v>
       </x:c>
       <x:c r="C13" s="15" t="str">
-        <x:v>Défini</x:v>
+        <x:v>Prototype</x:v>
       </x:c>
       <x:c r="D13" s="16" t="str">
         <x:v>Établi</x:v>
@@ -14951,7 +14959,7 @@
       <x:c r="J13" s="9" t="str"/>
       <x:c r="K13" s="9" t="str"/>
       <x:c r="L13" s="9" t="str">
-        <x:v>Livrable proposé : spécification EVO/lore/sc-afterwar-ref; brancher au registre de contenu de l'œuvre seulement après production.</x:v>
+        <x:v>Référence documentaire EVO-SC-AFTERWAR-REF consultable dans les lectures de src/chronicle-story.js, avec sources et progression séparée. Aucune scène, carte, animation ou incarnation de personnage n’est produite par cette fiche.</x:v>
       </x:c>
       <x:c r="M13" s="9" t="str">
         <x:v>Les résultats d’adaptation locaux convergent vers les faits de l’œuvre; les personnages absents ne deviennent pas des alliés disponibles.</x:v>
@@ -14966,14 +14974,14 @@
       <x:c r="Q13" s="9" t="str">
         <x:v>EVO-S-AUTHOR1</x:v>
       </x:c>
-      <x:c r="R13" s="20" t="str">
+      <x:c r="R13" s="9" t="str">
         <x:v>https://farawaypress.com/comics/masseffectevolution/masseffectevolution1/</x:v>
       </x:c>
-      <x:c r="S13" s="20" t="str">
-        <x:v>Ne remplace pas la lecture du numéro.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="54" customHeight="1">
+      <x:c r="S13" s="9" t="str">
+        <x:v>Ne remplace pas la lecture du numéro. Prototype limité à une paraphrase documentaire sourcée et aux références visitées. Les autres livrables de l’œuvre restent à produire ; les personnages mentionnés ne sont pas recrutables et les lieux cités ne deviennent pas des niveaux.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="82" customHeight="1">
       <x:c r="A14" s="19" t="str">
         <x:v>EVO-SC-ILLIUM-REF</x:v>
       </x:c>
@@ -14981,7 +14989,7 @@
         <x:v>Piste sur Illium</x:v>
       </x:c>
       <x:c r="C14" s="15" t="str">
-        <x:v>Défini</x:v>
+        <x:v>Prototype</x:v>
       </x:c>
       <x:c r="D14" s="17" t="str">
         <x:v>Établi</x:v>
@@ -15000,7 +15008,7 @@
       <x:c r="J14" s="7" t="str"/>
       <x:c r="K14" s="7" t="str"/>
       <x:c r="L14" s="7" t="str">
-        <x:v>Livrable proposé : spécification EVO/lore/sc-illium-ref; brancher au registre de contenu de l'œuvre seulement après production.</x:v>
+        <x:v>Référence documentaire EVO-SC-ILLIUM-REF consultable dans les lectures de src/chronicle-story.js, avec sources et progression séparée. Aucune scène, carte, animation ou incarnation de personnage n’est produite par cette fiche.</x:v>
       </x:c>
       <x:c r="M14" s="7" t="str">
         <x:v>Les résultats d’adaptation locaux convergent vers les faits de l’œuvre; les personnages absents ne deviennent pas des alliés disponibles.</x:v>
@@ -15015,14 +15023,14 @@
       <x:c r="Q14" s="7" t="str">
         <x:v>EVO-S-AUTHOR2</x:v>
       </x:c>
-      <x:c r="R14" s="21" t="str">
+      <x:c r="R14" s="7" t="str">
         <x:v>https://farawaypress.com/comics/masseffectevolution/masseffectevolution2/</x:v>
       </x:c>
-      <x:c r="S14" s="21" t="str">
-        <x:v>Ne remplace pas la lecture du numéro.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="54" customHeight="1">
+      <x:c r="S14" s="7" t="str">
+        <x:v>Ne remplace pas la lecture du numéro. Prototype limité à une paraphrase documentaire sourcée et aux références visitées. Les autres livrables de l’œuvre restent à produire ; les personnages mentionnés ne sont pas recrutables et les lieux cités ne deviennent pas des niveaux.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="82" customHeight="1">
       <x:c r="A15" s="18" t="str">
         <x:v>EVO-SC-PALAVEN-REF</x:v>
       </x:c>
@@ -15030,7 +15038,7 @@
         <x:v>Tradition et projet de Desolas</x:v>
       </x:c>
       <x:c r="C15" s="15" t="str">
-        <x:v>Défini</x:v>
+        <x:v>Prototype</x:v>
       </x:c>
       <x:c r="D15" s="16" t="str">
         <x:v>Établi</x:v>
@@ -15049,7 +15057,7 @@
       <x:c r="J15" s="9" t="str"/>
       <x:c r="K15" s="9" t="str"/>
       <x:c r="L15" s="9" t="str">
-        <x:v>Livrable proposé : spécification EVO/lore/sc-palaven-ref; brancher au registre de contenu de l'œuvre seulement après production.</x:v>
+        <x:v>Référence documentaire EVO-SC-PALAVEN-REF consultable dans les lectures de src/chronicle-story.js, avec sources et progression séparée. Aucune scène, carte, animation ou incarnation de personnage n’est produite par cette fiche.</x:v>
       </x:c>
       <x:c r="M15" s="9" t="str">
         <x:v>Les résultats d’adaptation locaux convergent vers les faits de l’œuvre; les personnages absents ne deviennent pas des alliés disponibles.</x:v>
@@ -15064,14 +15072,14 @@
       <x:c r="Q15" s="9" t="str">
         <x:v>EVO-S-AUTHOR3</x:v>
       </x:c>
-      <x:c r="R15" s="20" t="str">
+      <x:c r="R15" s="9" t="str">
         <x:v>https://farawaypress.com/comics/masseffectevolution/masseffectevolution3/</x:v>
       </x:c>
-      <x:c r="S15" s="20" t="str">
-        <x:v>Ne remplace pas la lecture du numéro.</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" ht="54" customHeight="1">
+      <x:c r="S15" s="9" t="str">
+        <x:v>Ne remplace pas la lecture du numéro. Prototype limité à une paraphrase documentaire sourcée et aux références visitées. Les autres livrables de l’œuvre restent à produire ; les personnages mentionnés ne sont pas recrutables et les lieux cités ne deviennent pas des niveaux.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="82" customHeight="1">
       <x:c r="A16" s="19" t="str">
         <x:v>EVO-SC-BREAK-REF</x:v>
       </x:c>
@@ -15079,7 +15087,7 @@
         <x:v>Rupture du contrôle</x:v>
       </x:c>
       <x:c r="C16" s="15" t="str">
-        <x:v>Défini</x:v>
+        <x:v>Prototype</x:v>
       </x:c>
       <x:c r="D16" s="17" t="str">
         <x:v>Établi</x:v>
@@ -15098,7 +15106,7 @@
       <x:c r="J16" s="7" t="str"/>
       <x:c r="K16" s="7" t="str"/>
       <x:c r="L16" s="7" t="str">
-        <x:v>Livrable proposé : spécification EVO/lore/sc-break-ref; brancher au registre de contenu de l'œuvre seulement après production.</x:v>
+        <x:v>Référence documentaire EVO-SC-BREAK-REF consultable dans les lectures de src/chronicle-story.js, avec sources et progression séparée. Aucune scène, carte, animation ou incarnation de personnage n’est produite par cette fiche.</x:v>
       </x:c>
       <x:c r="M16" s="7" t="str">
         <x:v>Les résultats d’adaptation locaux convergent vers les faits de l’œuvre; les personnages absents ne deviennent pas des alliés disponibles.</x:v>
@@ -15113,11 +15121,11 @@
       <x:c r="Q16" s="7" t="str">
         <x:v>EVO-S-AUTHOR4</x:v>
       </x:c>
-      <x:c r="R16" s="21" t="str">
+      <x:c r="R16" s="7" t="str">
         <x:v>https://farawaypress.com/comics/masseffectevolution/masseffectevolution4/</x:v>
       </x:c>
-      <x:c r="S16" s="21" t="str">
-        <x:v>Ne remplace pas la lecture du numéro.</x:v>
+      <x:c r="S16" s="7" t="str">
+        <x:v>Ne remplace pas la lecture du numéro. Prototype limité à une paraphrase documentaire sourcée et aux références visitées. Les autres livrables de l’œuvre restent à produire ; les personnages mentionnés ne sont pas recrutables et les lieux cités ne deviennent pas des niveaux.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -15152,7 +15160,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R56c2c2523b9c42da"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbe3e07c83bf34b03"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15292,61 +15300,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -15394,10 +15402,10 @@
       <x:c r="Q7" s="9" t="str">
         <x:v>EVO-S-EVA</x:v>
       </x:c>
-      <x:c r="R7" s="20" t="str">
+      <x:c r="R7" s="9" t="str">
         <x:v>https://masseffect.fandom.com/wiki/Eva_Cor%C3%A9</x:v>
       </x:c>
-      <x:c r="S7" s="20" t="str">
+      <x:c r="S7" s="9" t="str">
         <x:v>La géométrie jouable ci-dessous est originale et ne prétend pas reconstituer une carte officielle.</x:v>
       </x:c>
     </x:row>
@@ -15445,10 +15453,10 @@
       <x:c r="Q8" s="7" t="str">
         <x:v>EVO-S-AUTHOR2</x:v>
       </x:c>
-      <x:c r="R8" s="21" t="str">
+      <x:c r="R8" s="7" t="str">
         <x:v>https://farawaypress.com/comics/masseffectevolution/masseffectevolution2/</x:v>
       </x:c>
-      <x:c r="S8" s="21" t="str">
+      <x:c r="S8" s="7" t="str">
         <x:v>La géométrie jouable ci-dessous est originale et ne prétend pas reconstituer une carte officielle.</x:v>
       </x:c>
     </x:row>
@@ -15496,10 +15504,10 @@
       <x:c r="Q9" s="9" t="str">
         <x:v>EVO-S-AUTHOR2</x:v>
       </x:c>
-      <x:c r="R9" s="20" t="str">
+      <x:c r="R9" s="9" t="str">
         <x:v>https://farawaypress.com/comics/masseffectevolution/masseffectevolution2/</x:v>
       </x:c>
-      <x:c r="S9" s="20" t="str">
+      <x:c r="S9" s="9" t="str">
         <x:v>La géométrie jouable ci-dessous est originale et ne prétend pas reconstituer une carte officielle.</x:v>
       </x:c>
     </x:row>
@@ -15547,10 +15555,10 @@
       <x:c r="Q10" s="7" t="str">
         <x:v>EVO-S-AUTHOR3</x:v>
       </x:c>
-      <x:c r="R10" s="21" t="str">
+      <x:c r="R10" s="7" t="str">
         <x:v>https://farawaypress.com/comics/masseffectevolution/masseffectevolution3/</x:v>
       </x:c>
-      <x:c r="S10" s="21" t="str">
+      <x:c r="S10" s="7" t="str">
         <x:v>La géométrie jouable ci-dessous est originale et ne prétend pas reconstituer une carte officielle.</x:v>
       </x:c>
     </x:row>
@@ -15586,7 +15594,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdbcbae9d59dd4103"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc953ccda7e4048c3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15726,61 +15734,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -15832,8 +15840,8 @@
         <x:v>Plan original, dimensions à prototyper.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -15883,8 +15891,8 @@
         <x:v>Plan original, dimensions à prototyper.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -15934,8 +15942,8 @@
         <x:v>Plan original, dimensions à prototyper.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -15985,8 +15993,8 @@
         <x:v>Plan original, dimensions à prototyper.</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D10">
@@ -16020,7 +16028,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R271c84054e124ff4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd7f21c21c44d4f59"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16160,61 +16168,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -16264,8 +16272,8 @@
         <x:v>Raccord de gameplay original; ordre narratif selon les ancrages sourcés.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -16313,8 +16321,8 @@
         <x:v>Raccord de gameplay original; ordre narratif selon les ancrages sourcés.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -16362,8 +16370,8 @@
         <x:v>Raccord de gameplay original; ordre narratif selon les ancrages sourcés.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -16411,8 +16419,8 @@
         <x:v>Raccord de gameplay original; ordre narratif selon les ancrages sourcés.</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D10">
@@ -16446,7 +16454,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R75df04f82a84445c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8c032609e3004c7d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16586,61 +16594,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -16690,8 +16698,8 @@
         <x:v>Direction artistique originale, matériaux à confronter aux planches.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="68" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -16739,8 +16747,8 @@
         <x:v>Direction artistique originale, matériaux à confronter aux planches.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="68" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -16788,8 +16796,8 @@
         <x:v>Direction artistique originale, matériaux à confronter aux planches.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="68" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -16837,8 +16845,8 @@
         <x:v>Direction artistique originale, matériaux à confronter aux planches.</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D10">
@@ -16872,7 +16880,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R25ede505c5e54736"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd5c959a5f4754ca4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17012,61 +17020,61 @@
       <x:c r="S5" s="2"/>
     </x:row>
     <x:row r="6" ht="34" customHeight="1">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="28" t="str">
         <x:v>Identifiant</x:v>
       </x:c>
-      <x:c r="B6" s="31" t="str">
+      <x:c r="B6" s="29" t="str">
         <x:v>Élément</x:v>
       </x:c>
-      <x:c r="C6" s="31" t="str">
+      <x:c r="C6" s="29" t="str">
         <x:v>Contenu</x:v>
       </x:c>
-      <x:c r="D6" s="31" t="str">
+      <x:c r="D6" s="29" t="str">
         <x:v>Nature de la référence</x:v>
       </x:c>
-      <x:c r="E6" s="31" t="str">
+      <x:c r="E6" s="29" t="str">
         <x:v>Priorité</x:v>
       </x:c>
-      <x:c r="F6" s="31" t="str">
+      <x:c r="F6" s="29" t="str">
         <x:v>Fait ou hypothèse</x:v>
       </x:c>
-      <x:c r="G6" s="31" t="str">
+      <x:c r="G6" s="29" t="str">
         <x:v>Adaptation proposée</x:v>
       </x:c>
-      <x:c r="H6" s="31" t="str">
+      <x:c r="H6" s="29" t="str">
         <x:v>Règles et moveset proposés</x:v>
       </x:c>
-      <x:c r="I6" s="31" t="str">
+      <x:c r="I6" s="29" t="str">
         <x:v>Direction visuelle</x:v>
       </x:c>
-      <x:c r="J6" s="31" t="str">
+      <x:c r="J6" s="29" t="str">
         <x:v>Animation</x:v>
       </x:c>
-      <x:c r="K6" s="31" t="str">
+      <x:c r="K6" s="29" t="str">
         <x:v>Audio et accessibilité</x:v>
       </x:c>
-      <x:c r="L6" s="31" t="str">
+      <x:c r="L6" s="29" t="str">
         <x:v>Mise en œuvre prévue</x:v>
       </x:c>
-      <x:c r="M6" s="31" t="str">
+      <x:c r="M6" s="29" t="str">
         <x:v>Conditions et variantes</x:v>
       </x:c>
-      <x:c r="N6" s="31" t="str">
+      <x:c r="N6" s="29" t="str">
         <x:v>Critère d’acceptation</x:v>
       </x:c>
-      <x:c r="O6" s="31" t="str">
+      <x:c r="O6" s="29" t="str">
         <x:v>Dépendances</x:v>
       </x:c>
-      <x:c r="P6" s="31" t="str">
+      <x:c r="P6" s="29" t="str">
         <x:v>Repère dans l’œuvre</x:v>
       </x:c>
-      <x:c r="Q6" s="31" t="str">
+      <x:c r="Q6" s="29" t="str">
         <x:v>Sources</x:v>
       </x:c>
-      <x:c r="R6" s="31" t="str">
+      <x:c r="R6" s="29" t="str">
         <x:v>Sources URL</x:v>
       </x:c>
-      <x:c r="S6" s="32" t="str">
+      <x:c r="S6" s="30" t="str">
         <x:v>Notes et limites</x:v>
       </x:c>
     </x:row>
@@ -17120,8 +17128,8 @@
         <x:v>Accessoire ou interaction de production proposé; ne vaut pas relevé exhaustif de la planche.</x:v>
       </x:c>
       <x:c r="Q7" s="9" t="str"/>
-      <x:c r="R7" s="20" t="str"/>
-      <x:c r="S7" s="20" t="str"/>
+      <x:c r="R7" s="9" t="str"/>
+      <x:c r="S7" s="9" t="str"/>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="19" t="str">
@@ -17173,8 +17181,8 @@
         <x:v>Accessoire ou interaction de production proposé; ne vaut pas relevé exhaustif de la planche.</x:v>
       </x:c>
       <x:c r="Q8" s="7" t="str"/>
-      <x:c r="R8" s="21" t="str"/>
-      <x:c r="S8" s="21" t="str"/>
+      <x:c r="R8" s="7" t="str"/>
+      <x:c r="S8" s="7" t="str"/>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="18" t="str">
@@ -17226,8 +17234,8 @@
         <x:v>Accessoire ou interaction de production proposé; ne vaut pas relevé exhaustif de la planche.</x:v>
       </x:c>
       <x:c r="Q9" s="9" t="str"/>
-      <x:c r="R9" s="20" t="str"/>
-      <x:c r="S9" s="20" t="str"/>
+      <x:c r="R9" s="9" t="str"/>
+      <x:c r="S9" s="9" t="str"/>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="19" t="str">
@@ -17279,8 +17287,8 @@
         <x:v>Accessoire ou interaction de production proposé; ne vaut pas relevé exhaustif de la planche.</x:v>
       </x:c>
       <x:c r="Q10" s="7" t="str"/>
-      <x:c r="R10" s="21" t="str"/>
-      <x:c r="S10" s="21" t="str"/>
+      <x:c r="R10" s="7" t="str"/>
+      <x:c r="S10" s="7" t="str"/>
     </x:row>
     <x:row r="11" ht="54" customHeight="1">
       <x:c r="A11" s="18" t="str">
@@ -17332,8 +17340,8 @@
         <x:v>Accessoire ou interaction de production proposé; ne vaut pas relevé exhaustif de la planche.</x:v>
       </x:c>
       <x:c r="Q11" s="9" t="str"/>
-      <x:c r="R11" s="20" t="str"/>
-      <x:c r="S11" s="20" t="str"/>
+      <x:c r="R11" s="9" t="str"/>
+      <x:c r="S11" s="9" t="str"/>
     </x:row>
     <x:row r="12" ht="54" customHeight="1">
       <x:c r="A12" s="19" t="str">
@@ -17385,8 +17393,8 @@
         <x:v>Accessoire ou interaction de production proposé; ne vaut pas relevé exhaustif de la planche.</x:v>
       </x:c>
       <x:c r="Q12" s="7" t="str"/>
-      <x:c r="R12" s="21" t="str"/>
-      <x:c r="S12" s="21" t="str"/>
+      <x:c r="R12" s="7" t="str"/>
+      <x:c r="S12" s="7" t="str"/>
     </x:row>
   </x:sheetData>
   <x:conditionalFormatting sqref="D7:D12">
@@ -17420,7 +17428,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R45a693d3f1974543"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6f78fa1e91ce4cd5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Evolution_Production.xlsx
+++ b/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Evolution_Production.xlsx
@@ -2,34 +2,34 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Ref8da14d5c174291"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="R00075bfd6eda4eea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="Rb80973683d51416c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="R055f5de0fb934b7d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="R732799aab53643d6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="Rd66d8aa90a694082"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="Rc12349e6b87940a2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="Rf535ad4f275d4936"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="R1bb3edf44d0a476a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="R6b45b52bc165458c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="R5bba45d4e8c743aa"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="R8b83b7fd80074b25"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="Rff8a251197564f49"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="R049e1bc80b2940a5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="R2e321147539f4a2d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R0b7bf4a07df64309"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="R88c46a6cc38a4190"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="R3bc3721903ac407f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="R88e849d0638d49c6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="R100608afceeb4c68"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="Raa78634bc45341b9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="R67b6f9a0d0e44867"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="R91d9cc58999d4c6d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="R857eea84b5e34ace"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="Rce0f342c8f1546bb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="Re3d0de76b38c4de6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="Rf534406493534b2a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="R285ab1c1c9c74c3a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Re010776be6b8420d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="R0af04b37007849a1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="Rce414bd579c946eb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="Rcf0d0abd3c6b4c0a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="R57527daa68774ed3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="Red5d104693db4597"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="Rea6d1dfecf1d4912"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="R3a0cf94bda374279"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="Re8f7f75422de4fbf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="Rc20552f60deb4f9a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="Rc66e6559e5b6495a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="R841bb200b0634c9f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R7066af673022493f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="Rb26d8ab7af76471c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="R36f7aebb129b472a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R112f89536dc6445e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="R6860e16a4e974f20"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="Rf9caab1d98d341b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="Rff7383f17e8a44b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="R8e6f1a840b224bea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="R1208d1fd53994feb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="R09fda8b525eb4084"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="R412640a0278f4b39"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="R310a9e4b06a8401d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="R6ead3751ff5f41ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="Rbca9847241294702"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="R69b59e779ee54b87"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="R08a1fba987944029"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2385,11 +2385,11 @@
       </x:c>
       <x:c r="C12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$C$7:$C$16,"Défini")</x:f>
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$C$7:$C$16,"Prototype")</x:f>
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E12" s="37" t="n">
         <x:f>COUNTIFS('Especes_factions'!$C$7:$C$16,"Intégré")</x:f>
@@ -3672,11 +3672,11 @@
       </x:c>
       <x:c r="C37" s="39" t="n">
         <x:f>SUM(C10:C35)</x:f>
-        <x:v>118</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="D37" s="39" t="n">
         <x:f>SUM(D10:D35)</x:f>
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E37" s="39" t="n">
         <x:f>SUM(E10:E35)</x:f>
@@ -4195,7 +4195,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R02de9d748f7543c9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R673b1d9d93c94254"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4743,7 +4743,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2f1bcb26c01b47eb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1d4ba5913d9d47af"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5291,7 +5291,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0ef560463dba4161"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R36a1af8ea0a54162"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5839,7 +5839,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra97eea96c6854335"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd044dabeb0334f8a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6387,7 +6387,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re9bbf1169aff4f47"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf2fb04a874244f35"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6923,7 +6923,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcbd3ea89b26548c7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R42bb11c13ff140b0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7204,7 +7204,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdaff3fe6f6164cf2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8614ecec995a46fa"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7485,7 +7485,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R294f97c7f7cc4ada"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R453b528e5b4f4adb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7766,7 +7766,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8e14d12b30c54d80"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8142a2ea71f34851"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8102,7 +8102,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7a45620c17bb43fc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R787eeef4fc7f4b7b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8560,7 +8560,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9ab42619236045f7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra3c00a3de9014f5d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9108,7 +9108,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb688d2de175044fe"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re99500f6231b4615"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9695,7 +9695,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra09338c9a8a5420b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd537d679d9e5469d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10268,7 +10268,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0a9b345fdae24363"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R52ed6008c896426e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10804,7 +10804,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc237b08d3fc244cd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R31b4f3b94e4843fd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11246,7 +11246,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R813ce140fd764fdf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0652850a1f1d4d78"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11664,7 +11664,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R621f3d6d438241a3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdfe7be23eb35405c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12311,7 +12311,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf6ed1dc41fcf4913"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcab991e7992842d0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12631,7 +12631,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf8dc5d86474b4632"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfb7f5d44834c49ca"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12748,7 +12748,7 @@
         <x:v>Projet</x:v>
       </x:c>
       <x:c r="B10" s="7" t="str">
-        <x:v>122 fiches de production ; 4 fiches au stade Prototype de portée partielle. Les autres livrables restent des spécifications ; aucun achèvement intégral 1:1 revendiqué.</x:v>
+        <x:v>122 fiches de production ; 5 fiches au stade Prototype de portée partielle. Les autres livrables restent des spécifications ; aucun achèvement intégral 1:1 revendiqué.</x:v>
       </x:c>
       <x:c r="C10" s="2"/>
       <x:c r="D10" s="2"/>
@@ -13470,7 +13470,7 @@
         <x:v>Complément pouvoirs, modules et lectures</x:v>
       </x:c>
       <x:c r="B63" s="6" t="str">
-        <x:v>0 fiches de pouvoirs utilisées, 0 familles de modules préparables et 4 références consultables dans une lecture documentaire. Les chemins et preuves sont inscrits sur les seules lignes Prototype.</x:v>
+        <x:v>0 fiches de pouvoirs effectivement utilisées, 0 familles de modules préparables et 5 références au stade Prototype consultables dans des lectures documentaires. Les chemins et preuves sont inscrits sur les seules lignes Prototype.</x:v>
       </x:c>
       <x:c r="C63" s="6" t="str">
         <x:v>Arbres et progression complets, modèles et rangs exacts, campagnes et dialogues intégraux, niveaux et ressources visuelles propres à l’œuvre restent à réaliser ou vérifier. Les références lues ne rendent pas leurs personnages jouables.</x:v>
@@ -13479,10 +13479,16 @@
       <x:c r="E63" s="2"/>
       <x:c r="F63" s="2"/>
     </x:row>
-    <x:row r="64" ht="22" customHeight="1">
-      <x:c r="A64" s="2"/>
-      <x:c r="B64" s="2"/>
-      <x:c r="C64" s="2"/>
+    <x:row r="64" ht="96" customHeight="1">
+      <x:c r="A64" s="6" t="str">
+        <x:v>Complément lectures contextualisées</x:v>
+      </x:c>
+      <x:c r="B64" s="6" t="str">
+        <x:v>1 références supplémentaires au stade Prototype dans 1 parcours de lecture (1 pages de paraphrases documentaires sourcées), limités à leurs segments exacts.</x:v>
+      </x:c>
+      <x:c r="C64" s="6" t="str">
+        <x:v>Les faits, références, sources et réserves d’origine sont conservés. Ces lectures ne constituent ni un découpage intégral, ni une scène jouable, ni un recrutement ; modèles, voix et animations de l’œuvre ne sont pas produits.</x:v>
+      </x:c>
       <x:c r="D64" s="2"/>
       <x:c r="E64" s="2"/>
       <x:c r="F64" s="2"/>
@@ -14038,6 +14044,14 @@
       <x:c r="D133" s="2"/>
       <x:c r="E133" s="2"/>
       <x:c r="F133" s="2"/>
+    </x:row>
+    <x:row r="134" ht="22" customHeight="1">
+      <x:c r="A134" s="2"/>
+      <x:c r="B134" s="2"/>
+      <x:c r="C134" s="2"/>
+      <x:c r="D134" s="2"/>
+      <x:c r="E134" s="2"/>
+      <x:c r="F134" s="2"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14440,7 +14454,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1c314a50d05c4ca9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7fd103d9a7854d96"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14834,7 +14848,7 @@
         <x:v>Fait résumé brièvement; aucun dialogue ni découpage intégral du comic reproduit.</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="54" customHeight="1">
+    <x:row r="11" ht="82" customHeight="1">
       <x:c r="A11" s="18" t="str">
         <x:v>EVO-SC-RESIST-REF</x:v>
       </x:c>
@@ -14842,7 +14856,7 @@
         <x:v>Résistance sur Shanxi</x:v>
       </x:c>
       <x:c r="C11" s="15" t="str">
-        <x:v>Défini</x:v>
+        <x:v>Prototype</x:v>
       </x:c>
       <x:c r="D11" s="16" t="str">
         <x:v>Établi</x:v>
@@ -14861,7 +14875,7 @@
       <x:c r="J11" s="9" t="str"/>
       <x:c r="K11" s="9" t="str"/>
       <x:c r="L11" s="9" t="str">
-        <x:v>Livrable proposé : spécification EVO/lore/sc-resist-ref; brancher au registre de contenu de l'œuvre seulement après production.</x:v>
+        <x:v>Référence documentaire EVO-SC-RESIST-REF consultable dans les lectures evo-contact de src/chronicle-story.js, avec sources et progression séparée. Aucune scène, carte, animation ni incarnation de personnage produite par cette fiche.</x:v>
       </x:c>
       <x:c r="M11" s="9" t="str">
         <x:v>Les résultats d’adaptation locaux convergent vers les faits de l’œuvre; les personnages absents ne deviennent pas des alliés disponibles.</x:v>
@@ -14880,7 +14894,7 @@
         <x:v>https://farawaypress.com/comics/masseffectevolution/masseffectevolution1/</x:v>
       </x:c>
       <x:c r="S11" s="9" t="str">
-        <x:v>Ne remplace pas la lecture du numéro.</x:v>
+        <x:v>Ne remplace pas la lecture du numéro. Prototype limité à une paraphrase documentaire sourcée et aux références visitées ; pas de reproduction intégrale du récit. Une lecture n’accorde ni recrutement, équipement, victoire ni récompense de campagne.</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="54" customHeight="1">
@@ -15160,7 +15174,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbe3e07c83bf34b03"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc067d0920f9b4253"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15594,7 +15608,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc953ccda7e4048c3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra5ce699e80a344b4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16028,7 +16042,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd7f21c21c44d4f59"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R080cf6885f5b45ec"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16454,7 +16468,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8c032609e3004c7d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf6f86f94cc1d4b16"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16880,7 +16894,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd5c959a5f4754ca4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R22711e96ded94661"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17428,7 +17442,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6f78fa1e91ce4cd5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8040fdc2a0ad421a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Evolution_Production.xlsx
+++ b/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Evolution_Production.xlsx
@@ -2,34 +2,34 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Re010776be6b8420d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="R0af04b37007849a1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="Rce414bd579c946eb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="Rcf0d0abd3c6b4c0a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="R57527daa68774ed3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="Red5d104693db4597"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="Rea6d1dfecf1d4912"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="R3a0cf94bda374279"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="Re8f7f75422de4fbf"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="Rc20552f60deb4f9a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="Rc66e6559e5b6495a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="R841bb200b0634c9f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R7066af673022493f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="Rb26d8ab7af76471c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="R36f7aebb129b472a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R112f89536dc6445e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="R6860e16a4e974f20"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="Rf9caab1d98d341b9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="Rff7383f17e8a44b9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="R8e6f1a840b224bea"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="R1208d1fd53994feb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="R09fda8b525eb4084"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="R412640a0278f4b39"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="R310a9e4b06a8401d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="R6ead3751ff5f41ae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="Rbca9847241294702"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="R69b59e779ee54b87"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="R08a1fba987944029"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R9a24e183930c4a9d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="R86af58c711c447ef"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="R2fe921e3a5c54e0e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="Re81bfeb1e8f7440c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="Rc63fb9d25a834a9d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="R64be4d2fff5d4920"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="R8748ab097ce74e3e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="R4ed6f2ff007c4353"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="Ra7f8986b7f2b4cc7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="Red5b69df310b4ee8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="R71fba1f7539e459c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="Re8a64a9b23684c2d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="Rad1453b0d4004748"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="Re86a1361a180482d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="R23990f7b06774f4c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R9ce89ccc9fea45b7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="R34078ac49daf4d80"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="R6f4fc7fdd6af4f76"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="R78c0791371e341b4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="Rf8feb65eaa244b78"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="R4b6940ea8234488a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="R02009fd856464141"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="R9e2a1b73d1824c72"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="R22174f8868af49a4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="R50810ff71aef4ad0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="Re5a471ed63e64abe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="R724bef7972144951"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="R2666654140d04062"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4195,7 +4195,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R673b1d9d93c94254"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4b718e2f3c4a4423"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4743,7 +4743,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1d4ba5913d9d47af"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R775fc299af514db5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5291,7 +5291,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R36a1af8ea0a54162"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7c0919efdcc842eb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5839,7 +5839,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd044dabeb0334f8a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd626ec7a46f24da7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6387,7 +6387,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf2fb04a874244f35"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc94f0f20c0ee48b3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6923,7 +6923,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R42bb11c13ff140b0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd8441e311a4a428d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7204,7 +7204,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8614ecec995a46fa"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc79c89c60e7a41a8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7485,7 +7485,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R453b528e5b4f4adb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5e56fa1bfcf44763"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7766,7 +7766,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8142a2ea71f34851"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R83ebecadaa264f12"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8102,7 +8102,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R787eeef4fc7f4b7b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R311d0e343b864416"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8560,7 +8560,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra3c00a3de9014f5d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R669214a169974df7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9108,7 +9108,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re99500f6231b4615"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R737c3511fd214470"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9695,7 +9695,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd537d679d9e5469d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8ceabcd0bcda4b77"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10268,7 +10268,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R52ed6008c896426e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf46ffa4e72cc4840"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10804,7 +10804,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R31b4f3b94e4843fd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7d1a253b351546e1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11246,7 +11246,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0652850a1f1d4d78"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra831f28dc6be4b59"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11664,7 +11664,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdfe7be23eb35405c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R89a5a4ee49154fb9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12311,7 +12311,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcab991e7992842d0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R27833fec21484074"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12631,7 +12631,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfb7f5d44834c49ca"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd7d69639c2ef49f4"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14454,7 +14454,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7fd103d9a7854d96"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb67387accd204b6e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15174,7 +15174,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc067d0920f9b4253"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R63f44dd2c3124f8b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15608,7 +15608,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra5ce699e80a344b4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R549aaa29f17e4274"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16042,7 +16042,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R080cf6885f5b45ec"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra3bf934369be4057"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16468,7 +16468,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf6f86f94cc1d4b16"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R209110c1de614121"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16894,7 +16894,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R22711e96ded94661"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfd37e71ee0ff41a3"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17442,7 +17442,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8040fdc2a0ad421a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1ceaa7499a474c66"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Evolution_Production.xlsx
+++ b/docs/universe/outputs/relay-chronicles-20261022/Mass_Effect_Evolution_Production.xlsx
@@ -2,34 +2,34 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R9a24e183930c4a9d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="R86af58c711c447ef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="R2fe921e3a5c54e0e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="Re81bfeb1e8f7440c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="Rc63fb9d25a834a9d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="R64be4d2fff5d4920"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="R8748ab097ce74e3e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="R4ed6f2ff007c4353"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="Ra7f8986b7f2b4cc7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="Red5b69df310b4ee8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="R71fba1f7539e459c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="Re8a64a9b23684c2d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="Rad1453b0d4004748"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="Re86a1361a180482d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="R23990f7b06774f4c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R9ce89ccc9fea45b7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="R34078ac49daf4d80"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="R6f4fc7fdd6af4f76"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="R78c0791371e341b4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="Rf8feb65eaa244b78"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="R4b6940ea8234488a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="R02009fd856464141"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="R9e2a1b73d1824c72"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="R22174f8868af49a4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="R50810ff71aef4ad0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="Re5a471ed63e64abe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="R724bef7972144951"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="R2666654140d04062"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R7acaa89f064045db"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Personnages" sheetId="2" r:id="R4e5ac3a32e164fa4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PNJ" sheetId="3" r:id="R412d711fe31a4b84"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Especes_factions" sheetId="4" r:id="Rc2c6fe069d3b4db8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mondes" sheetId="5" r:id="R33123304b1e34e17"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Zones" sheetId="6" r:id="R0f98a58a9efb4a82"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Liaisons" sheetId="7" r:id="R05c82e471f9b4883"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Decors" sheetId="8" r:id="Rb2ff5797604f48ba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Props" sheetId="9" r:id="Rfefddf08838c4e71"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ennemis_boss" sheetId="10" r:id="Ra9e8389a069e4176"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missions" sheetId="11" r:id="R55e33116f1f74d99"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Secondaires_DLC" sheetId="12" r:id="R0cf1f23072224d8e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Choix_relations" sheetId="13" r:id="R21b9642d8c484402"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dialogues" sheetId="14" r:id="Rea494cc56ea64c1f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cinematiques" sheetId="15" r:id="Ra4a753522a4642aa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armes" sheetId="16" r:id="R938d4138581640c3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Armures_equipement" sheetId="17" r:id="Rcc844c5d19914819"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pouvoirs" sheetId="18" r:id="R03006bb1a2604a0e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_allies" sheetId="19" r:id="R2946d3ba1af0479d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Movesets_ennemis" sheetId="20" r:id="R9ce6287cc2534bc1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Animations" sheetId="21" r:id="R33d648b709804e9c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sprites" sheetId="22" r:id="R13f7630259274508"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFX" sheetId="23" r:id="R4a20cbc51ba04658"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audio" sheetId="24" r:id="R998d7f09546b42fb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UI_systemes" sheetId="25" r:id="R805ba35b939a424c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA" sheetId="26" r:id="R22592be0f89c43a9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Continuite" sheetId="27" r:id="R4607a4869522431e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guide" sheetId="28" r:id="R36f96e290a4f4c98"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -4195,7 +4195,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4b718e2f3c4a4423"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5da88b77128b4c25"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4743,7 +4743,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R775fc299af514db5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1cc243fcb9b74ff5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5291,7 +5291,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7c0919efdcc842eb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3fead4a5d1c54513"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5839,7 +5839,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd626ec7a46f24da7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb86b759e7ac144f6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6387,7 +6387,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc94f0f20c0ee48b3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rae5cf35304254c15"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6923,7 +6923,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd8441e311a4a428d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbd5e9e0ecf644f9c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7204,7 +7204,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc79c89c60e7a41a8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R61fc77a07e9d4a03"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7485,7 +7485,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R5e56fa1bfcf44763"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9b4865e4da694323"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7766,7 +7766,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R83ebecadaa264f12"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2ee1cfd755e544aa"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8102,7 +8102,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R311d0e343b864416"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd9da49101e30464e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8560,7 +8560,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R669214a169974df7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra29246d5328a4f3f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9108,7 +9108,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R737c3511fd214470"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf593f5e0456b4f73"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9695,7 +9695,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8ceabcd0bcda4b77"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0b416b5c674247ab"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10268,7 +10268,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf46ffa4e72cc4840"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R45cdb8a19d674eb0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -10804,7 +10804,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7d1a253b351546e1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R326b0b74c0c3422e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11246,7 +11246,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra831f28dc6be4b59"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3a1a33e3e03045b5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11664,7 +11664,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R89a5a4ee49154fb9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R30b9af1601f34c90"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12311,7 +12311,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R27833fec21484074"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd93378fe439742a7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12631,7 +12631,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd7d69639c2ef49f4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R33a2748d6fde43dd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14454,7 +14454,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb67387accd204b6e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R64bd4796f49e434d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15174,7 +15174,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R63f44dd2c3124f8b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R09f94ea2dc3846b7"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15608,7 +15608,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R549aaa29f17e4274"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0f3656262a4141de"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16042,7 +16042,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra3bf934369be4057"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R47dbbc91970c4509"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16468,7 +16468,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R209110c1de614121"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6427dae480ee45a1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16894,7 +16894,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfd37e71ee0ff41a3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6b9272bf5e1f4a1c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17442,7 +17442,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1ceaa7499a474c66"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re49ae1cab95f4bba"/>
   </x:tableParts>
 </x:worksheet>
 </file>